--- a/raw_data/3-128.xlsx
+++ b/raw_data/3-128.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHECK-main\CHECK-main\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7ED103-51FE-446F-A191-1F63C9E01143}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79B64DB-805C-4C2F-AD3B-560A02CFBC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="336">
   <si>
     <r>
       <rPr>
@@ -3539,6 +3539,182 @@
         <rFont val="Times New Roman"/>
       </rPr>
       <t>LF7F8(24B11CS212) -3098/ANK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF17F18(24B11CS213) -3045/VIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF11F12(15B11CI311) -3040/KSA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF21F22(24B11CS213) -244B/KSH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF7F8(24B11CS213) -3098/GAH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF21F22(15B11CI311) -244B/NFCS11</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TF21(15B11CI311) -3116/RKV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF24F25(24B11CS213) -3093/VKG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF17F18(15B11CI518) -3045/DTS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TF22(15B11CI311) -3117/NFCS17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TE4(24B11CS218)-3116/KALPANA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LF21F22(26B11CS216) -244B/AMS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TH1(15B11HS211) -3117/ALOK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TH3(15B11CI311) -3116/NFCS17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TF18(15B11CI518)-3116/NFCS16</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TH2(15B11HS211) -3117/PRV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TH4(25B11MA213)-/SREYA</t>
     </r>
   </si>
 </sst>
@@ -3739,7 +3915,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
@@ -3767,12 +3943,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4" shrinkToFit="1" readingOrder="1"/>
     </xf>
@@ -3782,10 +3952,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3794,41 +3964,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="6" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7" shrinkToFit="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" indent="5" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10" shrinkToFit="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="8" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="7" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
@@ -3842,14 +4006,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4155,7 +4346,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -4180,1111 +4371,1111 @@
   <sheetData>
     <row r="1" spans="1:17" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="37"/>
+      <c r="D1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
     </row>
     <row r="2" spans="1:17" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12" t="s">
+      <c r="E2" s="33"/>
+      <c r="F2" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="13" t="s">
+      <c r="I2" s="33"/>
+      <c r="J2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="13"/>
-      <c r="L2" s="12" t="s">
+      <c r="K2" s="21"/>
+      <c r="L2" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="12" t="s">
+      <c r="M2" s="33"/>
+      <c r="N2" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="12"/>
-      <c r="P2" s="12" t="s">
+      <c r="O2" s="33"/>
+      <c r="P2" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="12"/>
+      <c r="Q2" s="33"/>
     </row>
     <row r="3" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
-      <c r="Q3" s="15"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="25"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="25"/>
+      <c r="P3" s="25"/>
+      <c r="Q3" s="25"/>
     </row>
     <row r="4" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16" t="s">
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="25"/>
+      <c r="F4" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16" t="s">
+      <c r="G4" s="14"/>
+      <c r="H4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="17" t="s">
+      <c r="I4" s="14"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="17"/>
-      <c r="N4" s="16" t="s">
+      <c r="M4" s="15"/>
+      <c r="N4" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="16"/>
-      <c r="P4" s="13" t="s">
+      <c r="O4" s="14"/>
+      <c r="P4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="13"/>
+      <c r="Q4" s="21"/>
     </row>
     <row r="5" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="16" t="s">
+      <c r="C5" s="21"/>
+      <c r="D5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="16"/>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="18" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="18"/>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="13" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="13"/>
+      <c r="Q5" s="21"/>
     </row>
     <row r="6" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="11" t="s">
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="21" t="s">
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="21"/>
-      <c r="N6" s="21"/>
-      <c r="O6" s="21"/>
-      <c r="P6" s="17" t="s">
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="17"/>
+      <c r="Q6" s="15"/>
     </row>
     <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="17"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="22" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="16" t="s">
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="13" t="s">
+      <c r="M7" s="14"/>
+      <c r="N7" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="13"/>
-      <c r="P7" s="16" t="s">
+      <c r="O7" s="21"/>
+      <c r="P7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="16"/>
+      <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="16" t="s">
+      <c r="E8" s="21"/>
+      <c r="F8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16" t="s">
+      <c r="G8" s="14"/>
+      <c r="H8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="16" t="s">
+      <c r="I8" s="14"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="13" t="s">
+      <c r="M8" s="14"/>
+      <c r="N8" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="13"/>
-      <c r="P8" s="16" t="s">
+      <c r="O8" s="21"/>
+      <c r="P8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="16"/>
+      <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="13" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="16" t="s">
+      <c r="E9" s="21"/>
+      <c r="F9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16" t="s">
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="16" t="s">
+      <c r="I9" s="14"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="23" t="s">
+      <c r="M9" s="14"/>
+      <c r="N9" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="23"/>
-      <c r="P9" s="16" t="s">
+      <c r="O9" s="41"/>
+      <c r="P9" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="16"/>
+      <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16" t="s">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="16" t="s">
+      <c r="E10" s="14"/>
+      <c r="F10" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16" t="s">
+      <c r="G10" s="14"/>
+      <c r="H10" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="16" t="s">
+      <c r="I10" s="14"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16" t="s">
+      <c r="M10" s="14"/>
+      <c r="N10" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16" t="s">
+      <c r="O10" s="14"/>
+      <c r="P10" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="Q10" s="16"/>
+      <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="16" t="s">
+      <c r="C11" s="21"/>
+      <c r="D11" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16" t="s">
+      <c r="E11" s="14"/>
+      <c r="F11" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16" t="s">
+      <c r="G11" s="14"/>
+      <c r="H11" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="19"/>
-      <c r="L11" s="16" t="s">
+      <c r="I11" s="14"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="13" t="s">
+      <c r="M11" s="14"/>
+      <c r="N11" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13" t="s">
+      <c r="O11" s="21"/>
+      <c r="P11" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="13"/>
+      <c r="Q11" s="21"/>
     </row>
     <row r="12" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16" t="s">
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16" t="s">
+      <c r="G12" s="14"/>
+      <c r="H12" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="19"/>
-      <c r="K12" s="19"/>
-      <c r="L12" s="13" t="s">
+      <c r="I12" s="14"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13" t="s">
+      <c r="M12" s="21"/>
+      <c r="N12" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13" t="s">
+      <c r="O12" s="21"/>
+      <c r="P12" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="Q12" s="13"/>
+      <c r="Q12" s="21"/>
     </row>
     <row r="13" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="13" t="s">
+      <c r="E13" s="14"/>
+      <c r="F13" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13" t="s">
+      <c r="G13" s="21"/>
+      <c r="H13" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="16" t="s">
+      <c r="I13" s="21"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="13" t="s">
+      <c r="M13" s="14"/>
+      <c r="N13" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13" t="s">
+      <c r="O13" s="21"/>
+      <c r="P13" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="Q13" s="13"/>
+      <c r="Q13" s="21"/>
     </row>
     <row r="14" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="25"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="16"/>
-      <c r="F14" s="13" t="s">
+      <c r="E14" s="14"/>
+      <c r="F14" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="16" t="s">
+      <c r="G14" s="21"/>
+      <c r="H14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="19"/>
-      <c r="K14" s="19"/>
-      <c r="L14" s="16" t="s">
+      <c r="I14" s="14"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="13" t="s">
+      <c r="M14" s="14"/>
+      <c r="N14" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="O14" s="13"/>
-      <c r="P14" s="12" t="s">
+      <c r="O14" s="21"/>
+      <c r="P14" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="Q14" s="12"/>
+      <c r="Q14" s="33"/>
     </row>
     <row r="15" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="17" t="s">
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="17"/>
-      <c r="H15" s="16" t="s">
+      <c r="G15" s="15"/>
+      <c r="H15" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="17" t="s">
+      <c r="I15" s="14"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="M15" s="17"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
     </row>
     <row r="16" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="13" t="s">
+      <c r="C16" s="24"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
     </row>
     <row r="17" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
     </row>
     <row r="18" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="39" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
     </row>
     <row r="19" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="16" t="s">
+      <c r="A19" s="39"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16" t="s">
+      <c r="G19" s="14"/>
+      <c r="H19" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="I19" s="16"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="16" t="s">
+      <c r="I19" s="14"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="M19" s="16"/>
-      <c r="N19" s="13" t="s">
+      <c r="M19" s="14"/>
+      <c r="N19" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="O19" s="13"/>
-      <c r="P19" s="16" t="s">
+      <c r="O19" s="21"/>
+      <c r="P19" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="Q19" s="16"/>
+      <c r="Q19" s="14"/>
     </row>
     <row r="20" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13" t="s">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="13" t="s">
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="13"/>
-      <c r="P20" s="16" t="s">
+      <c r="O20" s="21"/>
+      <c r="P20" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="Q20" s="16"/>
+      <c r="Q20" s="14"/>
     </row>
     <row r="21" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12" t="s">
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="11" t="s">
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="M21" s="11"/>
-      <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
-      <c r="P21" s="16" t="s">
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="Q21" s="16"/>
+      <c r="Q21" s="14"/>
     </row>
     <row r="22" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="18" t="s">
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="18" t="s">
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18"/>
-      <c r="P22" s="23" t="s">
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="Q22" s="23"/>
+      <c r="Q22" s="41"/>
     </row>
     <row r="23" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="16" t="s">
+      <c r="C23" s="21"/>
+      <c r="D23" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="16"/>
+      <c r="E23" s="14"/>
       <c r="F23" s="22" t="s">
         <v>97</v>
       </c>
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="I23" s="22"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="17" t="s">
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="M23" s="17"/>
-      <c r="N23" s="13" t="s">
+      <c r="M23" s="15"/>
+      <c r="N23" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="O23" s="13"/>
-      <c r="P23" s="13" t="s">
+      <c r="O23" s="21"/>
+      <c r="P23" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="Q23" s="13"/>
+      <c r="Q23" s="21"/>
     </row>
     <row r="24" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="16" t="s">
+      <c r="C24" s="21"/>
+      <c r="D24" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="16"/>
+      <c r="E24" s="14"/>
       <c r="F24" s="22" t="s">
         <v>103</v>
       </c>
       <c r="G24" s="22"/>
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="16" t="s">
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17" t="s">
+      <c r="M24" s="14"/>
+      <c r="N24" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="O24" s="17"/>
-      <c r="P24" s="16" t="s">
+      <c r="O24" s="15"/>
+      <c r="P24" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="Q24" s="16"/>
+      <c r="Q24" s="14"/>
     </row>
     <row r="25" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="16" t="s">
+      <c r="C25" s="21"/>
+      <c r="D25" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="16"/>
+      <c r="E25" s="14"/>
       <c r="F25" s="22" t="s">
         <v>110</v>
       </c>
       <c r="G25" s="22"/>
       <c r="H25" s="22"/>
       <c r="I25" s="22"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="17" t="s">
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="M25" s="17"/>
-      <c r="N25" s="17" t="s">
+      <c r="M25" s="15"/>
+      <c r="N25" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="O25" s="17"/>
-      <c r="P25" s="16" t="s">
+      <c r="O25" s="15"/>
+      <c r="P25" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="Q25" s="16"/>
+      <c r="Q25" s="14"/>
     </row>
     <row r="26" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16" t="s">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16" t="s">
+      <c r="E26" s="14"/>
+      <c r="F26" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16" t="s">
+      <c r="G26" s="14"/>
+      <c r="H26" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="16" t="s">
+      <c r="I26" s="14"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16" t="s">
+      <c r="M26" s="14"/>
+      <c r="N26" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="16"/>
-      <c r="P26" s="13" t="s">
+      <c r="O26" s="14"/>
+      <c r="P26" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="Q26" s="13"/>
+      <c r="Q26" s="21"/>
     </row>
     <row r="27" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16" t="s">
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16" t="s">
+      <c r="E27" s="14"/>
+      <c r="F27" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16" t="s">
+      <c r="G27" s="14"/>
+      <c r="H27" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="16" t="s">
+      <c r="I27" s="14"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="M27" s="16"/>
-      <c r="N27" s="13" t="s">
+      <c r="M27" s="14"/>
+      <c r="N27" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="O27" s="13"/>
-      <c r="P27" s="13" t="s">
+      <c r="O27" s="21"/>
+      <c r="P27" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="Q27" s="13"/>
+      <c r="Q27" s="21"/>
     </row>
     <row r="28" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="16" t="s">
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16" t="s">
+      <c r="E28" s="14"/>
+      <c r="F28" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17" t="s">
+      <c r="G28" s="14"/>
+      <c r="H28" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="I28" s="17"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="19"/>
-      <c r="L28" s="16" t="s">
+      <c r="I28" s="15"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="M28" s="16"/>
-      <c r="N28" s="13" t="s">
+      <c r="M28" s="14"/>
+      <c r="N28" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="O28" s="13"/>
-      <c r="P28" s="16" t="s">
+      <c r="O28" s="21"/>
+      <c r="P28" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="Q28" s="16"/>
+      <c r="Q28" s="14"/>
     </row>
     <row r="29" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16" t="s">
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16" t="s">
+      <c r="E29" s="14"/>
+      <c r="F29" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16" t="s">
+      <c r="G29" s="14"/>
+      <c r="H29" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="L29" s="16" t="s">
+      <c r="I29" s="14"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="M29" s="16"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="15"/>
-      <c r="P29" s="16" t="s">
+      <c r="M29" s="14"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" s="16"/>
+      <c r="Q29" s="14"/>
     </row>
     <row r="30" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="13" t="s">
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="16" t="s">
+      <c r="E30" s="21"/>
+      <c r="F30" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="13" t="s">
+      <c r="G30" s="14"/>
+      <c r="H30" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="I30" s="13"/>
-      <c r="J30" s="19"/>
-      <c r="K30" s="19"/>
-      <c r="L30" s="16" t="s">
+      <c r="I30" s="21"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="M30" s="16"/>
-      <c r="N30" s="15"/>
-      <c r="O30" s="15"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="15"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
     </row>
     <row r="31" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16" t="s">
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16" t="s">
+      <c r="E31" s="14"/>
+      <c r="F31" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="19"/>
-      <c r="K31" s="19"/>
-      <c r="L31" s="20" t="s">
+      <c r="G31" s="14"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="15"/>
+      <c r="M31" s="19"/>
+      <c r="N31" s="19"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
     </row>
     <row r="32" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="17" t="s">
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G32" s="17"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="19"/>
-      <c r="K32" s="19"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
-      <c r="O32" s="15"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
     </row>
     <row r="33" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
-      <c r="O33" s="15"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="15"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
     </row>
     <row r="34" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="39" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="19"/>
-      <c r="K34" s="19"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="26"/>
-      <c r="O34" s="26"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
+      <c r="B34" s="25"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="30"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="31"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
     </row>
     <row r="35" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="24"/>
-      <c r="B35" s="16" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16" t="s">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="16"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="16" t="s">
+      <c r="E35" s="14"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="I35" s="16"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="18" t="s">
+      <c r="I35" s="14"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18"/>
-      <c r="P35" s="13" t="s">
+      <c r="M35" s="20"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="20"/>
+      <c r="P35" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="Q35" s="13"/>
+      <c r="Q35" s="21"/>
     </row>
     <row r="36" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="16" t="s">
+      <c r="C36" s="21"/>
+      <c r="D36" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="16"/>
-      <c r="F36" s="18" t="s">
+      <c r="E36" s="14"/>
+      <c r="F36" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G36" s="18"/>
-      <c r="H36" s="18"/>
-      <c r="I36" s="18"/>
-      <c r="J36" s="19"/>
-      <c r="K36" s="19"/>
-      <c r="L36" s="11" t="s">
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="13" t="s">
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="Q36" s="13"/>
+      <c r="Q36" s="21"/>
     </row>
     <row r="37" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="17" t="s">
+      <c r="C37" s="21"/>
+      <c r="D37" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="17"/>
-      <c r="F37" s="11" t="s">
+      <c r="E37" s="15"/>
+      <c r="F37" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="19"/>
-      <c r="K37" s="19"/>
-      <c r="L37" s="27" t="s">
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="16" t="s">
+      <c r="M37" s="40"/>
+      <c r="N37" s="40"/>
+      <c r="O37" s="40"/>
+      <c r="P37" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="Q37" s="16"/>
+      <c r="Q37" s="14"/>
     </row>
     <row r="38" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="16" t="s">
+      <c r="C38" s="21"/>
+      <c r="D38" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="18" t="s">
+      <c r="E38" s="14"/>
+      <c r="F38" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18"/>
-      <c r="J38" s="19"/>
-      <c r="K38" s="19"/>
-      <c r="L38" s="16" t="s">
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="M38" s="16"/>
-      <c r="N38" s="21" t="s">
+      <c r="M38" s="14"/>
+      <c r="N38" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="O38" s="21"/>
-      <c r="P38" s="21"/>
-      <c r="Q38" s="21"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
     </row>
     <row r="39" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16" t="s">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16" t="s">
+      <c r="E39" s="14"/>
+      <c r="F39" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="G39" s="16"/>
-      <c r="H39" s="16" t="s">
+      <c r="G39" s="14"/>
+      <c r="H39" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="I39" s="16"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="13" t="s">
+      <c r="I39" s="14"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="M39" s="13"/>
-      <c r="N39" s="27" t="s">
+      <c r="M39" s="21"/>
+      <c r="N39" s="40" t="s">
         <v>167</v>
       </c>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
+      <c r="O39" s="40"/>
+      <c r="P39" s="40"/>
+      <c r="Q39" s="40"/>
     </row>
     <row r="40" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16" t="s">
+      <c r="B40" s="25"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16" t="s">
+      <c r="E40" s="14"/>
+      <c r="F40" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="G40" s="16"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="19"/>
-      <c r="K40" s="19"/>
-      <c r="L40" s="16" t="s">
+      <c r="G40" s="14"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="25"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="M40" s="16"/>
+      <c r="M40" s="14"/>
       <c r="N40" s="22" t="s">
         <v>171</v>
       </c>
@@ -5293,123 +5484,123 @@
       <c r="Q40" s="22"/>
     </row>
     <row r="41" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="16" t="s">
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="13" t="s">
+      <c r="E41" s="14"/>
+      <c r="F41" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="16" t="s">
+      <c r="G41" s="21"/>
+      <c r="H41" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="I41" s="16"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="28" t="s">
+      <c r="I41" s="14"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="M41" s="28"/>
-      <c r="N41" s="28"/>
-      <c r="O41" s="28"/>
-      <c r="P41" s="13" t="s">
+      <c r="M41" s="23"/>
+      <c r="N41" s="23"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="Q41" s="13"/>
+      <c r="Q41" s="21"/>
     </row>
     <row r="42" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="13" t="s">
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="16" t="s">
+      <c r="E42" s="21"/>
+      <c r="F42" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16" t="s">
+      <c r="G42" s="14"/>
+      <c r="H42" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="16" t="s">
+      <c r="I42" s="14"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17" t="s">
+      <c r="M42" s="14"/>
+      <c r="N42" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="O42" s="17"/>
-      <c r="P42" s="16" t="s">
+      <c r="O42" s="15"/>
+      <c r="P42" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="Q42" s="16"/>
+      <c r="Q42" s="14"/>
     </row>
     <row r="43" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16" t="s">
+      <c r="B43" s="25"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="16" t="s">
+      <c r="E43" s="14"/>
+      <c r="F43" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="16" t="s">
+      <c r="G43" s="14"/>
+      <c r="H43" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="I43" s="16"/>
-      <c r="J43" s="19"/>
-      <c r="K43" s="19"/>
-      <c r="L43" s="17" t="s">
+      <c r="I43" s="14"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="M43" s="17"/>
-      <c r="N43" s="13" t="s">
+      <c r="M43" s="15"/>
+      <c r="N43" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="O43" s="13"/>
-      <c r="P43" s="13" t="s">
+      <c r="O43" s="21"/>
+      <c r="P43" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="Q43" s="13"/>
+      <c r="Q43" s="21"/>
     </row>
     <row r="44" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="16" t="s">
+      <c r="B44" s="25"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="G44" s="16"/>
-      <c r="H44" s="13" t="s">
+      <c r="G44" s="14"/>
+      <c r="H44" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="I44" s="13"/>
-      <c r="J44" s="19"/>
-      <c r="K44" s="19"/>
-      <c r="L44" s="16" t="s">
+      <c r="I44" s="21"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
+      <c r="L44" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="M44" s="16"/>
-      <c r="N44" s="13" t="s">
+      <c r="M44" s="14"/>
+      <c r="N44" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="O44" s="13"/>
-      <c r="P44" s="13" t="s">
+      <c r="O44" s="21"/>
+      <c r="P44" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="Q44" s="13"/>
+      <c r="Q44" s="21"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="7">
@@ -5418,1328 +5609,1722 @@
     </row>
     <row r="46" spans="1:17" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10" t="s">
+      <c r="C46" s="37"/>
+      <c r="D46" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
-      <c r="N46" s="10"/>
-      <c r="O46" s="10"/>
-      <c r="P46" s="10"/>
-      <c r="Q46" s="10"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="38"/>
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="38"/>
+      <c r="P46" s="38"/>
+      <c r="Q46" s="38"/>
     </row>
     <row r="47" spans="1:17" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="11"/>
-      <c r="D47" s="12" t="s">
+      <c r="C47" s="35"/>
+      <c r="D47" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12" t="s">
+      <c r="E47" s="33"/>
+      <c r="F47" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12" t="s">
+      <c r="G47" s="33"/>
+      <c r="H47" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="12"/>
-      <c r="J47" s="13" t="s">
+      <c r="I47" s="33"/>
+      <c r="J47" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="K47" s="13"/>
-      <c r="L47" s="12" t="s">
+      <c r="K47" s="21"/>
+      <c r="L47" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12" t="s">
+      <c r="M47" s="33"/>
+      <c r="N47" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12" t="s">
+      <c r="O47" s="33"/>
+      <c r="P47" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="Q47" s="12"/>
+      <c r="Q47" s="33"/>
     </row>
     <row r="48" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="16" t="s">
+      <c r="B48" s="25"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16" t="s">
+      <c r="G48" s="14"/>
+      <c r="H48" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="I48" s="16"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="13" t="s">
+      <c r="I48" s="14"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="21" t="s">
         <v>192</v>
       </c>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13" t="s">
+      <c r="M48" s="21"/>
+      <c r="N48" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="O48" s="13"/>
-      <c r="P48" s="13" t="s">
+      <c r="O48" s="21"/>
+      <c r="P48" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="Q48" s="13"/>
+      <c r="Q48" s="21"/>
     </row>
     <row r="49" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="13" t="s">
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16" t="s">
+      <c r="G49" s="21"/>
+      <c r="H49" s="25"/>
+      <c r="I49" s="25"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="O49" s="16"/>
-      <c r="P49" s="17" t="s">
+      <c r="O49" s="14"/>
+      <c r="P49" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="Q49" s="17"/>
+      <c r="Q49" s="15"/>
     </row>
     <row r="50" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
-      <c r="B50" s="15"/>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15"/>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="19"/>
-      <c r="L50" s="15"/>
-      <c r="M50" s="15"/>
-      <c r="N50" s="15"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="16" t="s">
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="25"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="32"/>
+      <c r="K50" s="32"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="25"/>
+      <c r="P50" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="Q50" s="16"/>
+      <c r="Q50" s="14"/>
     </row>
     <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15"/>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
-      <c r="H51" s="15"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="19"/>
-      <c r="L51" s="15"/>
-      <c r="M51" s="15"/>
-      <c r="N51" s="15"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="15"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="25"/>
+      <c r="H51" s="25"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="32"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="25"/>
+      <c r="P51" s="25"/>
+      <c r="Q51" s="25"/>
     </row>
     <row r="52" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="16" t="s">
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="16"/>
-      <c r="J52" s="19"/>
-      <c r="K52" s="19"/>
-      <c r="L52" s="25"/>
-      <c r="M52" s="25"/>
-      <c r="N52" s="26"/>
-      <c r="O52" s="26"/>
-      <c r="P52" s="15"/>
-      <c r="Q52" s="15"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="32"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="25"/>
+      <c r="Q52" s="25"/>
     </row>
     <row r="53" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="11" t="s">
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="19"/>
-      <c r="K53" s="19"/>
-      <c r="L53" s="28" t="s">
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="32"/>
+      <c r="K53" s="32"/>
+      <c r="L53" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="M53" s="28"/>
-      <c r="N53" s="28"/>
-      <c r="O53" s="28"/>
-      <c r="P53" s="13" t="s">
+      <c r="M53" s="23"/>
+      <c r="N53" s="23"/>
+      <c r="O53" s="23"/>
+      <c r="P53" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="Q53" s="13"/>
+      <c r="Q53" s="21"/>
     </row>
     <row r="54" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="18" t="s">
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="16" t="s">
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="M54" s="16"/>
-      <c r="N54" s="16" t="s">
+      <c r="M54" s="14"/>
+      <c r="N54" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="O54" s="16"/>
-      <c r="P54" s="16" t="s">
+      <c r="O54" s="14"/>
+      <c r="P54" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="Q54" s="16"/>
+      <c r="Q54" s="14"/>
     </row>
     <row r="55" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="16"/>
-      <c r="D55" s="13" t="s">
+      <c r="C55" s="14"/>
+      <c r="D55" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="17" t="s">
+      <c r="E55" s="21"/>
+      <c r="F55" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="16" t="s">
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="32"/>
+      <c r="L55" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="M55" s="16"/>
-      <c r="N55" s="20" t="s">
+      <c r="M55" s="14"/>
+      <c r="N55" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="O55" s="20"/>
-      <c r="P55" s="20"/>
-      <c r="Q55" s="20"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
     </row>
     <row r="56" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="C56" s="17"/>
-      <c r="D56" s="13" t="s">
+      <c r="C56" s="15"/>
+      <c r="D56" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="17" t="s">
+      <c r="E56" s="21"/>
+      <c r="F56" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="G56" s="17"/>
-      <c r="H56" s="16" t="s">
+      <c r="G56" s="15"/>
+      <c r="H56" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="I56" s="16"/>
-      <c r="J56" s="19"/>
-      <c r="K56" s="19"/>
-      <c r="L56" s="13" t="s">
+      <c r="I56" s="14"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="32"/>
+      <c r="L56" s="21" t="s">
         <v>214</v>
       </c>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
-      <c r="P56" s="13" t="s">
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="21"/>
+      <c r="P56" s="21" t="s">
         <v>215</v>
       </c>
-      <c r="Q56" s="13"/>
+      <c r="Q56" s="21"/>
     </row>
     <row r="57" spans="1:17" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="16" t="s">
+      <c r="C57" s="21"/>
+      <c r="D57" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16" t="s">
+      <c r="E57" s="14"/>
+      <c r="F57" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16" t="s">
+      <c r="G57" s="14"/>
+      <c r="H57" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="I57" s="16"/>
-      <c r="J57" s="19"/>
-      <c r="K57" s="19"/>
-      <c r="L57" s="17" t="s">
+      <c r="I57" s="14"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="32"/>
+      <c r="L57" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="M57" s="17"/>
-      <c r="N57" s="13" t="s">
+      <c r="M57" s="15"/>
+      <c r="N57" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="O57" s="13"/>
-      <c r="P57" s="16" t="s">
+      <c r="O57" s="21"/>
+      <c r="P57" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="Q57" s="16"/>
+      <c r="Q57" s="14"/>
     </row>
     <row r="58" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="17" t="s">
+      <c r="C58" s="21"/>
+      <c r="D58" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="E58" s="17"/>
-      <c r="F58" s="16" t="s">
+      <c r="E58" s="15"/>
+      <c r="F58" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16" t="s">
+      <c r="G58" s="14"/>
+      <c r="H58" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="I58" s="16"/>
-      <c r="J58" s="19"/>
-      <c r="K58" s="19"/>
-      <c r="L58" s="16" t="s">
+      <c r="I58" s="14"/>
+      <c r="J58" s="32"/>
+      <c r="K58" s="32"/>
+      <c r="L58" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="M58" s="16"/>
-      <c r="N58" s="13" t="s">
+      <c r="M58" s="14"/>
+      <c r="N58" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="O58" s="13"/>
-      <c r="P58" s="13" t="s">
+      <c r="O58" s="21"/>
+      <c r="P58" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="Q58" s="13"/>
+      <c r="Q58" s="21"/>
     </row>
     <row r="59" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="16" t="s">
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16" t="s">
+      <c r="E59" s="14"/>
+      <c r="F59" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16" t="s">
+      <c r="G59" s="14"/>
+      <c r="H59" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="I59" s="16"/>
-      <c r="J59" s="19"/>
-      <c r="K59" s="19"/>
-      <c r="L59" s="16" t="s">
+      <c r="I59" s="14"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="M59" s="16"/>
-      <c r="N59" s="13" t="s">
+      <c r="M59" s="14"/>
+      <c r="N59" s="21" t="s">
         <v>230</v>
       </c>
-      <c r="O59" s="13"/>
-      <c r="P59" s="13" t="s">
+      <c r="O59" s="21"/>
+      <c r="P59" s="21" t="s">
         <v>231</v>
       </c>
-      <c r="Q59" s="13"/>
+      <c r="Q59" s="21"/>
     </row>
     <row r="60" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="13"/>
-      <c r="D60" s="16" t="s">
+      <c r="C60" s="21"/>
+      <c r="D60" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16" t="s">
+      <c r="E60" s="14"/>
+      <c r="F60" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16" t="s">
+      <c r="G60" s="14"/>
+      <c r="H60" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="I60" s="16"/>
-      <c r="J60" s="19"/>
-      <c r="K60" s="19"/>
-      <c r="L60" s="16" t="s">
+      <c r="I60" s="14"/>
+      <c r="J60" s="32"/>
+      <c r="K60" s="32"/>
+      <c r="L60" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="M60" s="16"/>
-      <c r="N60" s="13" t="s">
+      <c r="M60" s="14"/>
+      <c r="N60" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="O60" s="13"/>
-      <c r="P60" s="13" t="s">
+      <c r="O60" s="21"/>
+      <c r="P60" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="Q60" s="13"/>
+      <c r="Q60" s="21"/>
     </row>
     <row r="61" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
-      <c r="B61" s="15"/>
-      <c r="C61" s="15"/>
-      <c r="D61" s="16" t="s">
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16" t="s">
+      <c r="E61" s="14"/>
+      <c r="F61" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="G61" s="16"/>
-      <c r="H61" s="13" t="s">
+      <c r="G61" s="14"/>
+      <c r="H61" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="I61" s="13"/>
-      <c r="J61" s="19"/>
-      <c r="K61" s="19"/>
-      <c r="L61" s="13" t="s">
+      <c r="I61" s="21"/>
+      <c r="J61" s="32"/>
+      <c r="K61" s="32"/>
+      <c r="L61" s="21" t="s">
         <v>240</v>
       </c>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13" t="s">
+      <c r="M61" s="21"/>
+      <c r="N61" s="21" t="s">
         <v>241</v>
       </c>
-      <c r="O61" s="13"/>
-      <c r="P61" s="13" t="s">
+      <c r="O61" s="21"/>
+      <c r="P61" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="Q61" s="13"/>
+      <c r="Q61" s="21"/>
     </row>
     <row r="62" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
-      <c r="B62" s="15"/>
-      <c r="C62" s="15"/>
-      <c r="D62" s="16" t="s">
+      <c r="B62" s="25"/>
+      <c r="C62" s="25"/>
+      <c r="D62" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="E62" s="16"/>
-      <c r="F62" s="13" t="s">
+      <c r="E62" s="14"/>
+      <c r="F62" s="21" t="s">
         <v>244</v>
       </c>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13" t="s">
+      <c r="G62" s="21"/>
+      <c r="H62" s="21" t="s">
         <v>245</v>
       </c>
-      <c r="I62" s="13"/>
-      <c r="J62" s="19"/>
-      <c r="K62" s="19"/>
-      <c r="L62" s="16" t="s">
+      <c r="I62" s="21"/>
+      <c r="J62" s="32"/>
+      <c r="K62" s="32"/>
+      <c r="L62" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="M62" s="16"/>
-      <c r="N62" s="15"/>
-      <c r="O62" s="15"/>
-      <c r="P62" s="16" t="s">
+      <c r="M62" s="14"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="25"/>
+      <c r="P62" s="14" t="s">
         <v>247</v>
       </c>
-      <c r="Q62" s="16"/>
+      <c r="Q62" s="14"/>
     </row>
     <row r="63" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
-      <c r="B63" s="15"/>
-      <c r="C63" s="15"/>
-      <c r="D63" s="15"/>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
-      <c r="H63" s="15"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="19"/>
-      <c r="K63" s="19"/>
-      <c r="L63" s="15"/>
-      <c r="M63" s="15"/>
-      <c r="N63" s="15"/>
-      <c r="O63" s="15"/>
-      <c r="P63" s="16" t="s">
+      <c r="B63" s="25"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="32"/>
+      <c r="K63" s="32"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="25"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="25"/>
+      <c r="P63" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="Q63" s="16"/>
+      <c r="Q63" s="14"/>
     </row>
     <row r="64" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
-      <c r="B64" s="15"/>
-      <c r="C64" s="15"/>
-      <c r="D64" s="15"/>
-      <c r="E64" s="15"/>
-      <c r="F64" s="13" t="s">
+      <c r="B64" s="25"/>
+      <c r="C64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="25"/>
+      <c r="F64" s="21" t="s">
         <v>248</v>
       </c>
-      <c r="G64" s="13"/>
-      <c r="H64" s="15"/>
-      <c r="I64" s="15"/>
-      <c r="J64" s="19"/>
-      <c r="K64" s="19"/>
-      <c r="L64" s="15"/>
-      <c r="M64" s="15"/>
-      <c r="N64" s="15"/>
-      <c r="O64" s="15"/>
-      <c r="P64" s="16" t="s">
+      <c r="G64" s="21"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="25"/>
+      <c r="J64" s="32"/>
+      <c r="K64" s="32"/>
+      <c r="L64" s="25"/>
+      <c r="M64" s="25"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="25"/>
+      <c r="P64" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="Q64" s="16"/>
+      <c r="Q64" s="14"/>
     </row>
     <row r="65" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15"/>
-      <c r="I65" s="15"/>
-      <c r="J65" s="19"/>
-      <c r="K65" s="19"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="15"/>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15"/>
-      <c r="Q65" s="15"/>
+      <c r="B65" s="25"/>
+      <c r="C65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="25"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="25"/>
+      <c r="H65" s="25"/>
+      <c r="I65" s="25"/>
+      <c r="J65" s="32"/>
+      <c r="K65" s="32"/>
+      <c r="L65" s="25"/>
+      <c r="M65" s="25"/>
+      <c r="N65" s="25"/>
+      <c r="O65" s="25"/>
+      <c r="P65" s="25"/>
+      <c r="Q65" s="25"/>
     </row>
     <row r="66" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B66" s="15"/>
-      <c r="C66" s="15"/>
-      <c r="D66" s="15"/>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
-      <c r="H66" s="15"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="19"/>
-      <c r="K66" s="19"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="15"/>
-      <c r="O66" s="15"/>
-      <c r="P66" s="15"/>
-      <c r="Q66" s="15"/>
+      <c r="B66" s="25"/>
+      <c r="C66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="25"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="25"/>
+      <c r="H66" s="25"/>
+      <c r="I66" s="25"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="32"/>
+      <c r="L66" s="25"/>
+      <c r="M66" s="25"/>
+      <c r="N66" s="25"/>
+      <c r="O66" s="25"/>
+      <c r="P66" s="25"/>
+      <c r="Q66" s="25"/>
     </row>
     <row r="67" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="29"/>
-      <c r="B67" s="15"/>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="16" t="s">
+      <c r="A67" s="34"/>
+      <c r="B67" s="25"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="I67" s="16"/>
-      <c r="J67" s="19"/>
-      <c r="K67" s="19"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="13" t="s">
+      <c r="I67" s="14"/>
+      <c r="J67" s="32"/>
+      <c r="K67" s="32"/>
+      <c r="L67" s="25"/>
+      <c r="M67" s="25"/>
+      <c r="N67" s="25"/>
+      <c r="O67" s="25"/>
+      <c r="P67" s="21" t="s">
         <v>250</v>
       </c>
-      <c r="Q67" s="13"/>
+      <c r="Q67" s="21"/>
     </row>
     <row r="68" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
-      <c r="B68" s="15"/>
-      <c r="C68" s="15"/>
-      <c r="D68" s="17" t="s">
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="E68" s="17"/>
-      <c r="F68" s="12" t="s">
+      <c r="E68" s="15"/>
+      <c r="F68" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="G68" s="12"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="12"/>
-      <c r="J68" s="19"/>
-      <c r="K68" s="19"/>
-      <c r="L68" s="16" t="s">
+      <c r="G68" s="33"/>
+      <c r="H68" s="33"/>
+      <c r="I68" s="33"/>
+      <c r="J68" s="32"/>
+      <c r="K68" s="32"/>
+      <c r="L68" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="M68" s="16"/>
-      <c r="N68" s="16" t="s">
+      <c r="M68" s="14"/>
+      <c r="N68" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="O68" s="16"/>
-      <c r="P68" s="13" t="s">
+      <c r="O68" s="14"/>
+      <c r="P68" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="Q68" s="13"/>
+      <c r="Q68" s="21"/>
     </row>
     <row r="69" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
-      <c r="B69" s="21" t="s">
+      <c r="B69" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21" t="s">
+      <c r="C69" s="24"/>
+      <c r="D69" s="24"/>
+      <c r="E69" s="24"/>
+      <c r="F69" s="24" t="s">
         <v>255</v>
       </c>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="19"/>
-      <c r="K69" s="19"/>
-      <c r="L69" s="11" t="s">
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="32"/>
+      <c r="K69" s="32"/>
+      <c r="L69" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="M69" s="11"/>
-      <c r="N69" s="11"/>
-      <c r="O69" s="11"/>
-      <c r="P69" s="16" t="s">
+      <c r="M69" s="35"/>
+      <c r="N69" s="35"/>
+      <c r="O69" s="35"/>
+      <c r="P69" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="Q69" s="16"/>
+      <c r="Q69" s="14"/>
     </row>
     <row r="70" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="C70" s="11"/>
-      <c r="D70" s="11"/>
-      <c r="E70" s="11"/>
-      <c r="F70" s="13" t="s">
+      <c r="C70" s="35"/>
+      <c r="D70" s="35"/>
+      <c r="E70" s="35"/>
+      <c r="F70" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="19"/>
-      <c r="K70" s="19"/>
-      <c r="L70" s="21" t="s">
+      <c r="G70" s="21"/>
+      <c r="H70" s="21"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="32"/>
+      <c r="K70" s="32"/>
+      <c r="L70" s="24" t="s">
         <v>259</v>
       </c>
-      <c r="M70" s="21"/>
-      <c r="N70" s="21"/>
-      <c r="O70" s="21"/>
-      <c r="P70" s="16" t="s">
+      <c r="M70" s="24"/>
+      <c r="N70" s="24"/>
+      <c r="O70" s="24"/>
+      <c r="P70" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="Q70" s="16"/>
+      <c r="Q70" s="14"/>
     </row>
     <row r="71" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="C71" s="13"/>
-      <c r="D71" s="16" t="s">
+      <c r="C71" s="21"/>
+      <c r="D71" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="E71" s="16"/>
-      <c r="F71" s="20" t="s">
+      <c r="E71" s="14"/>
+      <c r="F71" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="20"/>
-      <c r="I71" s="20"/>
-      <c r="J71" s="19"/>
-      <c r="K71" s="19"/>
-      <c r="L71" s="21" t="s">
+      <c r="G71" s="19"/>
+      <c r="H71" s="19"/>
+      <c r="I71" s="19"/>
+      <c r="J71" s="32"/>
+      <c r="K71" s="32"/>
+      <c r="L71" s="24" t="s">
         <v>264</v>
       </c>
-      <c r="M71" s="21"/>
-      <c r="N71" s="21"/>
-      <c r="O71" s="21"/>
-      <c r="P71" s="16" t="s">
+      <c r="M71" s="24"/>
+      <c r="N71" s="24"/>
+      <c r="O71" s="24"/>
+      <c r="P71" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="Q71" s="16"/>
+      <c r="Q71" s="14"/>
     </row>
     <row r="72" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="C72" s="13"/>
-      <c r="D72" s="16" t="s">
+      <c r="C72" s="21"/>
+      <c r="D72" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="E72" s="16"/>
-      <c r="F72" s="28" t="s">
+      <c r="E72" s="14"/>
+      <c r="F72" s="23" t="s">
         <v>267</v>
       </c>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-      <c r="J72" s="19"/>
-      <c r="K72" s="19"/>
-      <c r="L72" s="16" t="s">
+      <c r="G72" s="23"/>
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="32"/>
+      <c r="K72" s="32"/>
+      <c r="L72" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="M72" s="16"/>
-      <c r="N72" s="13" t="s">
+      <c r="M72" s="14"/>
+      <c r="N72" s="21" t="s">
         <v>269</v>
       </c>
-      <c r="O72" s="13"/>
-      <c r="P72" s="16" t="s">
+      <c r="O72" s="21"/>
+      <c r="P72" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="Q72" s="16"/>
+      <c r="Q72" s="14"/>
     </row>
     <row r="73" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="C73" s="13"/>
-      <c r="D73" s="16" t="s">
+      <c r="C73" s="21"/>
+      <c r="D73" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E73" s="16"/>
+      <c r="E73" s="14"/>
       <c r="F73" s="22" t="s">
         <v>274</v>
       </c>
       <c r="G73" s="22"/>
       <c r="H73" s="22"/>
       <c r="I73" s="22"/>
-      <c r="J73" s="19"/>
-      <c r="K73" s="19"/>
-      <c r="L73" s="16" t="s">
+      <c r="J73" s="32"/>
+      <c r="K73" s="32"/>
+      <c r="L73" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="M73" s="16"/>
-      <c r="N73" s="13" t="s">
+      <c r="M73" s="14"/>
+      <c r="N73" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="O73" s="13"/>
-      <c r="P73" s="16" t="s">
+      <c r="O73" s="21"/>
+      <c r="P73" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="Q73" s="16"/>
+      <c r="Q73" s="14"/>
     </row>
     <row r="74" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="C74" s="13"/>
-      <c r="D74" s="16" t="s">
+      <c r="C74" s="21"/>
+      <c r="D74" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E74" s="16"/>
-      <c r="F74" s="13" t="s">
+      <c r="E74" s="14"/>
+      <c r="F74" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="G74" s="13"/>
-      <c r="H74" s="16" t="s">
+      <c r="G74" s="21"/>
+      <c r="H74" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="I74" s="16"/>
-      <c r="J74" s="19"/>
-      <c r="K74" s="19"/>
-      <c r="L74" s="16" t="s">
+      <c r="I74" s="14"/>
+      <c r="J74" s="32"/>
+      <c r="K74" s="32"/>
+      <c r="L74" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="M74" s="16"/>
-      <c r="N74" s="13" t="s">
+      <c r="M74" s="14"/>
+      <c r="N74" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="O74" s="13"/>
-      <c r="P74" s="16" t="s">
+      <c r="O74" s="21"/>
+      <c r="P74" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="Q74" s="16"/>
+      <c r="Q74" s="14"/>
     </row>
     <row r="75" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
-      <c r="B75" s="15"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="16" t="s">
+      <c r="B75" s="25"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E75" s="16"/>
-      <c r="F75" s="17" t="s">
+      <c r="E75" s="14"/>
+      <c r="F75" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="G75" s="17"/>
-      <c r="H75" s="16" t="s">
+      <c r="G75" s="15"/>
+      <c r="H75" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="I75" s="16"/>
-      <c r="J75" s="19"/>
-      <c r="K75" s="19"/>
-      <c r="L75" s="13" t="s">
+      <c r="I75" s="14"/>
+      <c r="J75" s="32"/>
+      <c r="K75" s="32"/>
+      <c r="L75" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="M75" s="13"/>
-      <c r="N75" s="12" t="s">
+      <c r="M75" s="21"/>
+      <c r="N75" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="O75" s="12"/>
-      <c r="P75" s="13" t="s">
+      <c r="O75" s="33"/>
+      <c r="P75" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="Q75" s="13"/>
+      <c r="Q75" s="21"/>
     </row>
     <row r="76" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
-      <c r="B76" s="15"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="16" t="s">
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="E76" s="16"/>
-      <c r="F76" s="16" t="s">
+      <c r="E76" s="14"/>
+      <c r="F76" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="G76" s="16"/>
-      <c r="H76" s="16" t="s">
+      <c r="G76" s="14"/>
+      <c r="H76" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="I76" s="16"/>
-      <c r="J76" s="19"/>
-      <c r="K76" s="19"/>
-      <c r="L76" s="17" t="s">
+      <c r="I76" s="14"/>
+      <c r="J76" s="32"/>
+      <c r="K76" s="32"/>
+      <c r="L76" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="M76" s="17"/>
-      <c r="N76" s="16" t="s">
+      <c r="M76" s="15"/>
+      <c r="N76" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="O76" s="16"/>
-      <c r="P76" s="16" t="s">
+      <c r="O76" s="14"/>
+      <c r="P76" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="Q76" s="16"/>
+      <c r="Q76" s="14"/>
     </row>
     <row r="77" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
-      <c r="B77" s="15"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="13" t="s">
+      <c r="B77" s="25"/>
+      <c r="C77" s="25"/>
+      <c r="D77" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="E77" s="13"/>
-      <c r="F77" s="17" t="s">
+      <c r="E77" s="21"/>
+      <c r="F77" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17" t="s">
+      <c r="G77" s="15"/>
+      <c r="H77" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="I77" s="17"/>
-      <c r="J77" s="19"/>
-      <c r="K77" s="19"/>
-      <c r="L77" s="17" t="s">
+      <c r="I77" s="15"/>
+      <c r="J77" s="32"/>
+      <c r="K77" s="32"/>
+      <c r="L77" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="M77" s="17"/>
-      <c r="N77" s="17" t="s">
+      <c r="M77" s="15"/>
+      <c r="N77" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="O77" s="17"/>
-      <c r="P77" s="13" t="s">
+      <c r="O77" s="15"/>
+      <c r="P77" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="Q77" s="13"/>
+      <c r="Q77" s="21"/>
     </row>
     <row r="78" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="13" t="s">
+      <c r="B78" s="25"/>
+      <c r="C78" s="25"/>
+      <c r="D78" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="E78" s="13"/>
-      <c r="F78" s="16" t="s">
+      <c r="E78" s="21"/>
+      <c r="F78" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="G78" s="16"/>
-      <c r="H78" s="13" t="s">
+      <c r="G78" s="14"/>
+      <c r="H78" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="I78" s="13"/>
-      <c r="J78" s="19"/>
-      <c r="K78" s="19"/>
-      <c r="L78" s="17" t="s">
+      <c r="I78" s="21"/>
+      <c r="J78" s="32"/>
+      <c r="K78" s="32"/>
+      <c r="L78" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="M78" s="17"/>
-      <c r="N78" s="13" t="s">
+      <c r="M78" s="15"/>
+      <c r="N78" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="O78" s="13"/>
-      <c r="P78" s="15"/>
-      <c r="Q78" s="15"/>
+      <c r="O78" s="21"/>
+      <c r="P78" s="25"/>
+      <c r="Q78" s="25"/>
     </row>
     <row r="79" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
-      <c r="H79" s="16" t="s">
+      <c r="B79" s="25"/>
+      <c r="C79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="25"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="25"/>
+      <c r="H79" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="I79" s="16"/>
-      <c r="J79" s="19"/>
-      <c r="K79" s="19"/>
-      <c r="L79" s="16" t="s">
+      <c r="I79" s="14"/>
+      <c r="J79" s="32"/>
+      <c r="K79" s="32"/>
+      <c r="L79" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="M79" s="16"/>
-      <c r="N79" s="13" t="s">
+      <c r="M79" s="14"/>
+      <c r="N79" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="O79" s="13"/>
-      <c r="P79" s="15"/>
-      <c r="Q79" s="15"/>
+      <c r="O79" s="21"/>
+      <c r="P79" s="25"/>
+      <c r="Q79" s="25"/>
     </row>
     <row r="80" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
-      <c r="B80" s="15"/>
-      <c r="C80" s="15"/>
-      <c r="D80" s="15"/>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
-      <c r="H80" s="17" t="s">
+      <c r="B80" s="25"/>
+      <c r="C80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="25"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="25"/>
+      <c r="H80" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="I80" s="17"/>
-      <c r="J80" s="19"/>
-      <c r="K80" s="19"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="15"/>
-      <c r="O80" s="15"/>
-      <c r="P80" s="15"/>
-      <c r="Q80" s="15"/>
+      <c r="I80" s="15"/>
+      <c r="J80" s="32"/>
+      <c r="K80" s="32"/>
+      <c r="L80" s="25"/>
+      <c r="M80" s="25"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="25"/>
+      <c r="P80" s="25"/>
+      <c r="Q80" s="25"/>
     </row>
     <row r="81" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
-      <c r="B81" s="15"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="30"/>
-      <c r="K81" s="30"/>
-      <c r="L81" s="15"/>
-      <c r="M81" s="15"/>
-      <c r="N81" s="15"/>
-      <c r="O81" s="15"/>
-      <c r="P81" s="15"/>
-      <c r="Q81" s="15"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="25"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="25"/>
+      <c r="H81" s="25"/>
+      <c r="I81" s="25"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="25"/>
+      <c r="M81" s="25"/>
+      <c r="N81" s="25"/>
+      <c r="O81" s="25"/>
+      <c r="P81" s="25"/>
+      <c r="Q81" s="25"/>
     </row>
     <row r="82" spans="1:17" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B82" s="15"/>
-      <c r="C82" s="15"/>
-      <c r="D82" s="15"/>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="31"/>
-      <c r="K82" s="31"/>
-      <c r="L82" s="32"/>
-      <c r="M82" s="32"/>
-      <c r="N82" s="32"/>
-      <c r="O82" s="32"/>
-      <c r="P82" s="33"/>
-      <c r="Q82" s="33"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="25"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="27"/>
+      <c r="L82" s="28"/>
+      <c r="M82" s="28"/>
+      <c r="N82" s="28"/>
+      <c r="O82" s="28"/>
+      <c r="P82" s="29"/>
+      <c r="Q82" s="29"/>
     </row>
     <row r="83" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="26"/>
-      <c r="E83" s="26"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
       <c r="F83" s="22" t="s">
         <v>304</v>
       </c>
       <c r="G83" s="22"/>
       <c r="H83" s="22"/>
       <c r="I83" s="22"/>
-      <c r="J83" s="31"/>
-      <c r="K83" s="31"/>
-      <c r="L83" s="32"/>
-      <c r="M83" s="32"/>
-      <c r="N83" s="32"/>
-      <c r="O83" s="32"/>
-      <c r="P83" s="33"/>
-      <c r="Q83" s="33"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
+      <c r="L83" s="28"/>
+      <c r="M83" s="28"/>
+      <c r="N83" s="28"/>
+      <c r="O83" s="28"/>
+      <c r="P83" s="29"/>
+      <c r="Q83" s="29"/>
     </row>
     <row r="84" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="23" t="s">
         <v>305</v>
       </c>
-      <c r="C84" s="28"/>
-      <c r="D84" s="28"/>
-      <c r="E84" s="28"/>
-      <c r="F84" s="21" t="s">
+      <c r="C84" s="23"/>
+      <c r="D84" s="23"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="24" t="s">
         <v>306</v>
       </c>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="21"/>
-      <c r="J84" s="34"/>
-      <c r="K84" s="34"/>
-      <c r="L84" s="35"/>
-      <c r="M84" s="35"/>
-      <c r="N84" s="35"/>
-      <c r="O84" s="35"/>
-      <c r="P84" s="36"/>
-      <c r="Q84" s="36"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="24"/>
+      <c r="I84" s="24"/>
+      <c r="J84" s="16"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="17"/>
+      <c r="N84" s="17"/>
+      <c r="O84" s="17"/>
+      <c r="P84" s="18"/>
+      <c r="Q84" s="18"/>
     </row>
     <row r="85" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="20" t="s">
+      <c r="C85" s="20"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="19" t="s">
         <v>308</v>
       </c>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="34"/>
-      <c r="K85" s="34"/>
-      <c r="L85" s="35"/>
-      <c r="M85" s="35"/>
-      <c r="N85" s="35"/>
-      <c r="O85" s="35"/>
-      <c r="P85" s="36"/>
-      <c r="Q85" s="36"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="16"/>
+      <c r="K85" s="16"/>
+      <c r="L85" s="17"/>
+      <c r="M85" s="17"/>
+      <c r="N85" s="17"/>
+      <c r="O85" s="17"/>
+      <c r="P85" s="18"/>
+      <c r="Q85" s="18"/>
     </row>
     <row r="86" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
-      <c r="B86" s="20" t="s">
+      <c r="B86" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="18" t="s">
+      <c r="C86" s="19"/>
+      <c r="D86" s="19"/>
+      <c r="E86" s="19"/>
+      <c r="F86" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="G86" s="18"/>
-      <c r="H86" s="18"/>
-      <c r="I86" s="18"/>
-      <c r="J86" s="34"/>
-      <c r="K86" s="34"/>
-      <c r="L86" s="35"/>
-      <c r="M86" s="35"/>
-      <c r="N86" s="35"/>
-      <c r="O86" s="35"/>
-      <c r="P86" s="36"/>
-      <c r="Q86" s="36"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="16"/>
+      <c r="K86" s="16"/>
+      <c r="L86" s="17"/>
+      <c r="M86" s="17"/>
+      <c r="N86" s="17"/>
+      <c r="O86" s="17"/>
+      <c r="P86" s="18"/>
+      <c r="Q86" s="18"/>
     </row>
     <row r="87" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13" t="s">
+      <c r="C87" s="21"/>
+      <c r="D87" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="E87" s="13"/>
+      <c r="E87" s="21"/>
       <c r="F87" s="22" t="s">
         <v>312</v>
       </c>
       <c r="G87" s="22"/>
       <c r="H87" s="22"/>
       <c r="I87" s="22"/>
-      <c r="J87" s="34"/>
-      <c r="K87" s="34"/>
-      <c r="L87" s="35"/>
-      <c r="M87" s="35"/>
-      <c r="N87" s="35"/>
-      <c r="O87" s="35"/>
-      <c r="P87" s="36"/>
-      <c r="Q87" s="36"/>
+      <c r="J87" s="16"/>
+      <c r="K87" s="16"/>
+      <c r="L87" s="17"/>
+      <c r="M87" s="17"/>
+      <c r="N87" s="17"/>
+      <c r="O87" s="17"/>
+      <c r="P87" s="18"/>
+      <c r="Q87" s="18"/>
     </row>
     <row r="88" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
-      <c r="B88" s="16" t="s">
+      <c r="B88" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="C88" s="16"/>
-      <c r="D88" s="16" t="s">
+      <c r="C88" s="14"/>
+      <c r="D88" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="16" t="s">
+      <c r="E88" s="14"/>
+      <c r="F88" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="G88" s="16"/>
-      <c r="H88" s="17" t="s">
+      <c r="G88" s="14"/>
+      <c r="H88" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="I88" s="17"/>
-      <c r="J88" s="34"/>
-      <c r="K88" s="34"/>
-      <c r="L88" s="35"/>
-      <c r="M88" s="35"/>
-      <c r="N88" s="35"/>
-      <c r="O88" s="35"/>
-      <c r="P88" s="36"/>
-      <c r="Q88" s="36"/>
+      <c r="I88" s="15"/>
+      <c r="J88" s="16"/>
+      <c r="K88" s="16"/>
+      <c r="L88" s="17"/>
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+      <c r="O88" s="17"/>
+      <c r="P88" s="18"/>
+      <c r="Q88" s="18"/>
     </row>
     <row r="89" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="16" t="s">
+      <c r="B89" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C89" s="16"/>
-      <c r="D89" s="16" t="s">
+      <c r="C89" s="14"/>
+      <c r="D89" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="E89" s="16"/>
-      <c r="F89" s="16" t="s">
+      <c r="E89" s="14"/>
+      <c r="F89" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="G89" s="16"/>
-      <c r="H89" s="16" t="s">
+      <c r="G89" s="14"/>
+      <c r="H89" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="I89" s="16"/>
-      <c r="J89" s="34"/>
-      <c r="K89" s="34"/>
-      <c r="L89" s="35"/>
-      <c r="M89" s="35"/>
-      <c r="N89" s="35"/>
-      <c r="O89" s="35"/>
-      <c r="P89" s="36"/>
-      <c r="Q89" s="36"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="17"/>
+      <c r="M89" s="17"/>
+      <c r="N89" s="17"/>
+      <c r="O89" s="17"/>
+      <c r="P89" s="18"/>
+      <c r="Q89" s="18"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A90" s="7">
-        <v>2</v>
-      </c>
+      <c r="A90" s="7"/>
+      <c r="C90" s="9"/>
+      <c r="E90" s="10"/>
+      <c r="G90" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="I90" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="J90" s="14"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C91" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="G91" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="I91" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="J91" s="15"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C92" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="G92" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="I92" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="J92" s="14"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C93" s="11" t="s">
+        <v>325</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>326</v>
+      </c>
+      <c r="G93" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="I93" s="1"/>
+      <c r="J93" s="13"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C94" s="11" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="G94" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="I94" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="J94" s="14"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C95" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="G95" s="11" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C96" s="2"/>
+      <c r="G96" s="11" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C97" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="631">
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="N88:O88"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="L89:M89"/>
-    <mergeCell ref="N89:O89"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="F86:I86"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="L87:M87"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="F84:I84"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="N85:O85"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="L81:M81"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="J82:K83"/>
-    <mergeCell ref="L82:M83"/>
-    <mergeCell ref="N82:O83"/>
-    <mergeCell ref="P82:Q83"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="N79:O79"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="N77:O77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="N76:O76"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="F72:I72"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:I70"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="L70:O70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="F71:I71"/>
-    <mergeCell ref="J71:K71"/>
-    <mergeCell ref="L71:O71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:I69"/>
+  <mergeCells count="635">
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="I92:J92"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:Q1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K4"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:O9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="N10:O10"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="N11:O11"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="N12:O12"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="N14:O14"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="N15:O15"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="N16:O16"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K19"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="N24:O24"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="N28:O28"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="N29:O29"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="N30:O30"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="J34:K35"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="L35:O35"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N39:Q39"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:O37"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="L41:O41"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:E38"/>
+    <mergeCell ref="F38:I38"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:Q46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="J47:K47"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="N47:O47"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J49:K49"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="J50:K50"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="J51:K52"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:O53"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="F54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:I55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="N55:Q55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="L56:O56"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="J57:K57"/>
+    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="J58:K58"/>
+    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="L59:M59"/>
+    <mergeCell ref="N59:O59"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="J60:K60"/>
+    <mergeCell ref="L60:M60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="J64:K64"/>
+    <mergeCell ref="L64:M64"/>
+    <mergeCell ref="N64:O64"/>
+    <mergeCell ref="P64:Q64"/>
     <mergeCell ref="J69:K69"/>
     <mergeCell ref="L69:O69"/>
     <mergeCell ref="P69:Q69"/>
@@ -6764,462 +7349,157 @@
     <mergeCell ref="F67:G67"/>
     <mergeCell ref="H67:I67"/>
     <mergeCell ref="L67:M67"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:O56"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:Q46"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="N40:Q40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="L41:O41"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="N38:Q38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K35"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="L35:O35"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K19"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:Q1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:I70"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="L70:O70"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="F71:I71"/>
+    <mergeCell ref="J71:K71"/>
+    <mergeCell ref="L71:O71"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="F72:I72"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="L72:M72"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:I73"/>
+    <mergeCell ref="J73:K73"/>
+    <mergeCell ref="L73:M73"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="F68:I68"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:I69"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="L75:M75"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="L76:M76"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="J77:K77"/>
+    <mergeCell ref="L77:M77"/>
+    <mergeCell ref="N77:O77"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="J78:K78"/>
+    <mergeCell ref="L78:M78"/>
+    <mergeCell ref="N78:O78"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="L79:M79"/>
+    <mergeCell ref="N79:O79"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:I80"/>
+    <mergeCell ref="J80:K80"/>
+    <mergeCell ref="L80:M80"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="J81:K81"/>
+    <mergeCell ref="L81:M81"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="J82:K83"/>
+    <mergeCell ref="L82:M83"/>
+    <mergeCell ref="N82:O83"/>
+    <mergeCell ref="P82:Q83"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="F84:I84"/>
+    <mergeCell ref="J84:K84"/>
+    <mergeCell ref="L84:M84"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="F85:I85"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="L85:M85"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="F86:I86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:I87"/>
+    <mergeCell ref="J87:K87"/>
+    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="N87:O87"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:I88"/>
+    <mergeCell ref="J88:K88"/>
+    <mergeCell ref="L88:M88"/>
+    <mergeCell ref="N88:O88"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="N89:O89"/>
+    <mergeCell ref="P89:Q89"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/raw_data/3-128.xlsx
+++ b/raw_data/3-128.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CHECK-main\CHECK-main\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79B64DB-805C-4C2F-AD3B-560A02CFBC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7542D58-52A6-4E98-9F37-146B506F0D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="494">
   <si>
     <r>
       <rPr>
@@ -3715,6 +3715,1744 @@
         <rFont val="Times New Roman"/>
       </rPr>
       <t>TH4(25B11MA213)-/SREYA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Facu1ty Abbreviation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>COURSE CODE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>COURSE TITLE</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>26B11MA222</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Mathematica1 and Statistica1 Foundations for</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>LKK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Lakhveer Kaur</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SAK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Satyendra Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Computationa1 Inte11igence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AMB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Amita Bhagat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>DKA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Divya Kaushik</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>26B11CS216</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Artificia1 Inte11igence</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>KKS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Kam1esh Kumar Shuk1a</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>PRK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Priyanka Kwatra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>26B15CS216</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Artificia1 Inte11igence Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>NEA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Neha Ah1awat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>VAT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Vinay Anand Tikkiwa1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>26B15CS217</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Python Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ANK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ankit</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AJK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ajit Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B11CS223</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Software Engineering</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AHR</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ashish Sharma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ADP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Aditi Priya</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B15CS214</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Unix Programming Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>HMA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Himanshu Agraw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ANU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Anshu1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>15B11MA301</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Probabi1ity and Random Processes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>KNS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Kedar Nath</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>TWT</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Twink1e Tyagi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B11EC211</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>E1ectronic Devices and Circuits</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>MGO</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Mukta Goya1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>KSA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Krishna Asawa</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>18B11EC215</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Digita1 Circuit Design</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>NRP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Neeraj Pathak</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>MKS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Mukesh Saraswat</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B15EC211</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>E1ectronic Devices and Circuits Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AKANSHA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Tarkeshwar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>RSK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Rashmi Kushwah</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>18B15EC215</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Digita1 Circuit Design Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ADS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Aditi Sharma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AKB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Akansha Bhardwaj</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B11CS218</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Data Structures and A1gorithm Design</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AYP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ayushi Pandey</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B15CS218</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Data Structures and A1gorithm Design Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>DVP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Devpriya Soni</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ICY</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ishwar Chandra Yadav</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>19B13BT211</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Environmenta1 Studies</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>GAH</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Gaurav Sinha</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SVS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>25B11MA213</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Mathematica1 Foundations for Artificia1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Sajai Veer Singh</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Inte11igence and Data Science</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>JRD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Janardhan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>EKS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ekta Srivastava</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B11CS212</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Theory of Computation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>AMA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Amba Aggarwa1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>15B11CI311</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Data Structures</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SGU</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Shruti Gupta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>ANB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Anshu Banwari</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>15B17CI371</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Data Structures Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>VIS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Vikas Sharma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SHV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Shweta Verma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B11CS213</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Database Management Systems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SAV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Sakshi Varshney</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>PRV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Praveen Kumar Sharma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B15CS213</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Database Management Systems Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>VKG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Vicky Gupta</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>UMK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Umesh Khanduri</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SHP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Shivani Pant</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>NMD</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Noor Muhammad</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B15CS215</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Object Oriented Programming using Java</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>MAP</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Mahesh Pandey</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>SHA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Shreya</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t xml:space="preserve"> Aron</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>15B11HS211</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Economics</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>MAK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Manoj Kumar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>PLV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Pa11avi</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>25B11EC311</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Digita1 Systems and Computer Organization</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>DKS</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Dharmendra Kumar Sharma</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>PSK</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>25B15EC311</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Digita1 Systems and Computer Organisation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Piyush Kushwah</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>RGA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Ragini</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>PRM</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>Prakhar Mishra</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>24B25CS214</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+      </rPr>
+      <t>IT Infrastructure and Communication Lab</t>
     </r>
   </si>
 </sst>
@@ -3722,7 +5460,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -3751,6 +5489,12 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
+    <font>
+      <b/>
+      <sz val="6"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -3765,7 +5509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -3911,11 +5655,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
@@ -3937,10 +5712,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3952,10 +5748,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3964,35 +5760,41 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="6" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
+      <alignment horizontal="left" vertical="center" indent="7" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="9" shrinkToFit="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="10" shrinkToFit="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="8" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="7" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
@@ -4006,41 +5808,44 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="4" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="10" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4346,7 +6151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q97"/>
+  <dimension ref="A1:R130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" customWidth="1"/>
@@ -4357,3149 +6162,4624 @@
     <col min="6" max="6" width="0.6640625" customWidth="1"/>
     <col min="7" max="7" width="20.44140625" customWidth="1"/>
     <col min="8" max="8" width="0.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" customWidth="1"/>
-    <col min="10" max="10" width="0.6640625" customWidth="1"/>
-    <col min="11" max="11" width="17.44140625" customWidth="1"/>
-    <col min="12" max="12" width="0.6640625" customWidth="1"/>
-    <col min="13" max="13" width="20" customWidth="1"/>
-    <col min="14" max="14" width="0.6640625" customWidth="1"/>
-    <col min="15" max="15" width="21.77734375" customWidth="1"/>
-    <col min="16" max="16" width="0.6640625" customWidth="1"/>
-    <col min="17" max="17" width="21.44140625" customWidth="1"/>
-    <col min="18" max="18" width="0.6640625" customWidth="1"/>
+    <col min="9" max="9" width="5.21875" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" customWidth="1"/>
+    <col min="11" max="11" width="0.6640625" customWidth="1"/>
+    <col min="12" max="12" width="17.44140625" customWidth="1"/>
+    <col min="13" max="13" width="0.6640625" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="0.6640625" customWidth="1"/>
+    <col min="16" max="16" width="21.77734375" customWidth="1"/>
+    <col min="17" max="17" width="0.6640625" customWidth="1"/>
+    <col min="18" max="18" width="21.44140625" customWidth="1"/>
+    <col min="19" max="19" width="0.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="32.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38" t="s">
+      <c r="C1" s="14"/>
+      <c r="D1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-    </row>
-    <row r="2" spans="1:17" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+    </row>
+    <row r="2" spans="1:18" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="33" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33" t="s">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="33"/>
-      <c r="J2" s="21" t="s">
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="33" t="s">
+      <c r="L2" s="18"/>
+      <c r="M2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33" t="s">
+      <c r="N2" s="17"/>
+      <c r="O2" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33" t="s">
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="Q2" s="33"/>
-    </row>
-    <row r="3" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R2" s="17"/>
+    </row>
+    <row r="3" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="36"/>
-      <c r="K3" s="36"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-    </row>
-    <row r="4" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+    </row>
+    <row r="4" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="14" t="s">
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14" t="s">
+      <c r="G4" s="21"/>
+      <c r="H4" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="15" t="s">
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="15"/>
-      <c r="N4" s="14" t="s">
+      <c r="N4" s="22"/>
+      <c r="O4" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="14"/>
-      <c r="P4" s="21" t="s">
+      <c r="P4" s="21"/>
+      <c r="Q4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="21"/>
-    </row>
-    <row r="5" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R4" s="18"/>
+    </row>
+    <row r="5" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="21"/>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="21"/>
+      <c r="F5" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="20" t="s">
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="21" t="s">
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="21"/>
-    </row>
-    <row r="6" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R5" s="18"/>
+    </row>
+    <row r="6" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="35" t="s">
+      <c r="C6" s="25"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="24" t="s">
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="15" t="s">
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="15"/>
-    </row>
-    <row r="7" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R6" s="22"/>
+    </row>
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="15" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="22" t="s">
+      <c r="E7" s="22"/>
+      <c r="F7" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="14" t="s">
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="14"/>
-      <c r="N7" s="21" t="s">
+      <c r="N7" s="21"/>
+      <c r="O7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O7" s="21"/>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="18"/>
+      <c r="Q7" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="Q7" s="14"/>
-    </row>
-    <row r="8" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R7" s="21"/>
+    </row>
+    <row r="8" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="21"/>
-      <c r="F8" s="14" t="s">
+      <c r="E8" s="18"/>
+      <c r="F8" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14" t="s">
+      <c r="G8" s="21"/>
+      <c r="H8" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="14" t="s">
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="14"/>
-      <c r="N8" s="21" t="s">
+      <c r="N8" s="21"/>
+      <c r="O8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="O8" s="21"/>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="18"/>
+      <c r="Q8" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="Q8" s="14"/>
-    </row>
-    <row r="9" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R8" s="21"/>
+    </row>
+    <row r="9" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="21" t="s">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="21"/>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="18"/>
+      <c r="F9" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="21"/>
+      <c r="H9" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="14" t="s">
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="14"/>
-      <c r="N9" s="41" t="s">
+      <c r="N9" s="21"/>
+      <c r="O9" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="41"/>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="28"/>
+      <c r="Q9" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="14"/>
-    </row>
-    <row r="10" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="14" t="s">
+      <c r="R9" s="21"/>
+    </row>
+    <row r="10" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14" t="s">
+      <c r="E10" s="21"/>
+      <c r="F10" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14" t="s">
+      <c r="G10" s="21"/>
+      <c r="H10" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="32"/>
-      <c r="L10" s="14" t="s">
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14" t="s">
+      <c r="N10" s="21"/>
+      <c r="O10" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14" t="s">
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="Q10" s="14"/>
-    </row>
-    <row r="11" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R10" s="21"/>
+    </row>
+    <row r="11" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="21"/>
-      <c r="D11" s="14" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14" t="s">
+      <c r="E11" s="21"/>
+      <c r="F11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14" t="s">
+      <c r="G11" s="21"/>
+      <c r="H11" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="32"/>
-      <c r="L11" s="14" t="s">
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="14"/>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="21"/>
+      <c r="O11" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="21" t="s">
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="Q11" s="21"/>
-    </row>
-    <row r="12" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R11" s="18"/>
+    </row>
+    <row r="12" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
+      <c r="E12" s="21"/>
+      <c r="F12" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14" t="s">
+      <c r="G12" s="21"/>
+      <c r="H12" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="32"/>
-      <c r="L12" s="21" t="s">
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="M12" s="21"/>
-      <c r="N12" s="21" t="s">
+      <c r="N12" s="18"/>
+      <c r="O12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="21"/>
-      <c r="P12" s="21" t="s">
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="Q12" s="21"/>
-    </row>
-    <row r="13" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R12" s="18"/>
+    </row>
+    <row r="13" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="14" t="s">
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E13" s="14"/>
-      <c r="F13" s="21" t="s">
+      <c r="E13" s="21"/>
+      <c r="F13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21" t="s">
+      <c r="G13" s="18"/>
+      <c r="H13" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="14" t="s">
+      <c r="I13" s="18"/>
+      <c r="J13" s="18"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="M13" s="14"/>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="21"/>
+      <c r="O13" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21" t="s">
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="Q13" s="21"/>
-    </row>
-    <row r="14" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R13" s="18"/>
+    </row>
+    <row r="14" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="14" t="s">
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="14"/>
-      <c r="F14" s="21" t="s">
+      <c r="E14" s="21"/>
+      <c r="F14" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="14" t="s">
+      <c r="G14" s="18"/>
+      <c r="H14" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="32"/>
-      <c r="K14" s="32"/>
-      <c r="L14" s="14" t="s">
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="14"/>
-      <c r="N14" s="21" t="s">
+      <c r="N14" s="21"/>
+      <c r="O14" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="O14" s="21"/>
-      <c r="P14" s="33" t="s">
+      <c r="P14" s="18"/>
+      <c r="Q14" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="Q14" s="33"/>
-    </row>
-    <row r="15" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R14" s="17"/>
+    </row>
+    <row r="15" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="15" t="s">
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="14" t="s">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="15" t="s">
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-    </row>
-    <row r="16" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N15" s="22"/>
+      <c r="O15" s="20"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+    </row>
+    <row r="16" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="21" t="s">
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-    </row>
-    <row r="17" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="20"/>
+      <c r="O16" s="20"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+    </row>
+    <row r="17" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-    </row>
-    <row r="18" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="20"/>
+      <c r="O17" s="20"/>
+      <c r="P17" s="20"/>
+      <c r="Q17" s="20"/>
+      <c r="R17" s="20"/>
+    </row>
+    <row r="18" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-    </row>
-    <row r="19" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="39"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="14" t="s">
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="20"/>
+      <c r="O18" s="20"/>
+      <c r="P18" s="20"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20"/>
+    </row>
+    <row r="19" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="29"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14" t="s">
+      <c r="G19" s="21"/>
+      <c r="H19" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="14" t="s">
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="M19" s="14"/>
-      <c r="N19" s="21" t="s">
+      <c r="N19" s="21"/>
+      <c r="O19" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="O19" s="21"/>
-      <c r="P19" s="14" t="s">
+      <c r="P19" s="18"/>
+      <c r="Q19" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="Q19" s="14"/>
-    </row>
-    <row r="20" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R19" s="21"/>
+    </row>
+    <row r="20" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="21"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="21" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="21" t="s">
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="20"/>
+      <c r="N20" s="20"/>
+      <c r="O20" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="O20" s="21"/>
-      <c r="P20" s="14" t="s">
+      <c r="P20" s="18"/>
+      <c r="Q20" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="Q20" s="14"/>
-    </row>
-    <row r="21" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R20" s="21"/>
+    </row>
+    <row r="21" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="33" t="s">
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="32"/>
-      <c r="L21" s="35" t="s">
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="M21" s="35"/>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="14" t="s">
+      <c r="N21" s="16"/>
+      <c r="O21" s="16"/>
+      <c r="P21" s="16"/>
+      <c r="Q21" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="Q21" s="14"/>
-    </row>
-    <row r="22" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R21" s="21"/>
+    </row>
+    <row r="22" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="20" t="s">
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="20" t="s">
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="41" t="s">
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="Q22" s="41"/>
-    </row>
-    <row r="23" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R22" s="28"/>
+    </row>
+    <row r="23" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="21"/>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="18"/>
+      <c r="D23" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="22" t="s">
+      <c r="E23" s="21"/>
+      <c r="F23" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="32"/>
-      <c r="K23" s="32"/>
-      <c r="L23" s="15" t="s">
+      <c r="G23" s="27"/>
+      <c r="H23" s="27"/>
+      <c r="I23" s="27"/>
+      <c r="J23" s="27"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="M23" s="15"/>
-      <c r="N23" s="21" t="s">
+      <c r="N23" s="22"/>
+      <c r="O23" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="O23" s="21"/>
-      <c r="P23" s="21" t="s">
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="Q23" s="21"/>
-    </row>
-    <row r="24" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R23" s="18"/>
+    </row>
+    <row r="24" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="21"/>
-      <c r="D24" s="14" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="22" t="s">
+      <c r="E24" s="21"/>
+      <c r="F24" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="14" t="s">
+      <c r="G24" s="27"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="27"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="M24" s="14"/>
-      <c r="N24" s="15" t="s">
+      <c r="N24" s="21"/>
+      <c r="O24" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="O24" s="15"/>
-      <c r="P24" s="14" t="s">
+      <c r="P24" s="22"/>
+      <c r="Q24" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="Q24" s="14"/>
-    </row>
-    <row r="25" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="21" t="s">
+      <c r="R24" s="21"/>
+    </row>
+    <row r="25" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="18"/>
+      <c r="D25" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="22" t="s">
+      <c r="E25" s="21"/>
+      <c r="F25" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="32"/>
-      <c r="L25" s="15" t="s">
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="27"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15" t="s">
+      <c r="N25" s="22"/>
+      <c r="O25" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="O25" s="15"/>
-      <c r="P25" s="14" t="s">
+      <c r="P25" s="22"/>
+      <c r="Q25" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="Q25" s="14"/>
-    </row>
-    <row r="26" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="14" t="s">
+      <c r="R25" s="21"/>
+    </row>
+    <row r="26" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="21"/>
+      <c r="D26" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14" t="s">
+      <c r="E26" s="21"/>
+      <c r="F26" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14" t="s">
+      <c r="G26" s="21"/>
+      <c r="H26" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="32"/>
-      <c r="L26" s="14" t="s">
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14" t="s">
+      <c r="N26" s="21"/>
+      <c r="O26" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="O26" s="14"/>
-      <c r="P26" s="21" t="s">
+      <c r="P26" s="21"/>
+      <c r="Q26" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="Q26" s="21"/>
-    </row>
-    <row r="27" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R26" s="18"/>
+    </row>
+    <row r="27" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="14" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14" t="s">
+      <c r="E27" s="21"/>
+      <c r="F27" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14" t="s">
+      <c r="G27" s="21"/>
+      <c r="H27" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="I27" s="14"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="14" t="s">
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="M27" s="14"/>
-      <c r="N27" s="21" t="s">
+      <c r="N27" s="21"/>
+      <c r="O27" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21" t="s">
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="Q27" s="21"/>
-    </row>
-    <row r="28" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R27" s="18"/>
+    </row>
+    <row r="28" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="14" t="s">
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="G28" s="14"/>
-      <c r="H28" s="15" t="s">
+      <c r="G28" s="21"/>
+      <c r="H28" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="I28" s="15"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="14" t="s">
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="M28" s="14"/>
-      <c r="N28" s="21" t="s">
+      <c r="N28" s="21"/>
+      <c r="O28" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="O28" s="21"/>
-      <c r="P28" s="14" t="s">
+      <c r="P28" s="18"/>
+      <c r="Q28" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="Q28" s="14"/>
-    </row>
-    <row r="29" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R28" s="21"/>
+    </row>
+    <row r="29" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="14" t="s">
+      <c r="B29" s="20"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="21"/>
+      <c r="F29" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14" t="s">
+      <c r="G29" s="21"/>
+      <c r="H29" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="14" t="s">
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="M29" s="14"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="14" t="s">
+      <c r="N29" s="21"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="Q29" s="14"/>
-    </row>
-    <row r="30" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R29" s="21"/>
+    </row>
+    <row r="30" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="21" t="s">
+      <c r="B30" s="20"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="21"/>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="18"/>
+      <c r="F30" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="14"/>
-      <c r="H30" s="21" t="s">
+      <c r="G30" s="21"/>
+      <c r="H30" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="I30" s="21"/>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="14" t="s">
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M30" s="14"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-    </row>
-    <row r="31" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N30" s="21"/>
+      <c r="O30" s="20"/>
+      <c r="P30" s="20"/>
+      <c r="Q30" s="20"/>
+      <c r="R30" s="20"/>
+    </row>
+    <row r="31" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="20"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14" t="s">
+      <c r="E31" s="21"/>
+      <c r="F31" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="G31" s="14"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="32"/>
-      <c r="K31" s="32"/>
-      <c r="L31" s="19" t="s">
+      <c r="G31" s="21"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="M31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
       <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-    </row>
-    <row r="32" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q31" s="20"/>
+      <c r="R31" s="20"/>
+    </row>
+    <row r="32" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="15" t="s">
+      <c r="B32" s="20"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="G32" s="15"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="32"/>
-      <c r="K32" s="32"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-    </row>
-    <row r="33" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G32" s="22"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="20"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="20"/>
+      <c r="P32" s="20"/>
+      <c r="Q32" s="20"/>
+      <c r="R32" s="20"/>
+    </row>
+    <row r="33" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="32"/>
-      <c r="K33" s="32"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="25"/>
-      <c r="Q33" s="25"/>
-    </row>
-    <row r="34" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="39" t="s">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="20"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="20"/>
+      <c r="P33" s="20"/>
+      <c r="Q33" s="20"/>
+      <c r="R33" s="20"/>
+    </row>
+    <row r="34" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="30"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
       <c r="M34" s="30"/>
-      <c r="N34" s="31"/>
+      <c r="N34" s="30"/>
       <c r="O34" s="31"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-    </row>
-    <row r="35" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="39"/>
-      <c r="B35" s="14" t="s">
+      <c r="P34" s="31"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+    </row>
+    <row r="35" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="29"/>
+      <c r="B35" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14" t="s">
+      <c r="C35" s="21"/>
+      <c r="D35" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="14" t="s">
+      <c r="E35" s="21"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="32"/>
-      <c r="K35" s="32"/>
-      <c r="L35" s="20" t="s">
+      <c r="I35" s="21"/>
+      <c r="J35" s="21"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="M35" s="20"/>
-      <c r="N35" s="20"/>
-      <c r="O35" s="20"/>
-      <c r="P35" s="21" t="s">
+      <c r="N35" s="23"/>
+      <c r="O35" s="23"/>
+      <c r="P35" s="23"/>
+      <c r="Q35" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="Q35" s="21"/>
-    </row>
-    <row r="36" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R35" s="18"/>
+    </row>
+    <row r="36" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="C36" s="21"/>
-      <c r="D36" s="14" t="s">
+      <c r="C36" s="18"/>
+      <c r="D36" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E36" s="14"/>
-      <c r="F36" s="20" t="s">
+      <c r="E36" s="21"/>
+      <c r="F36" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="32"/>
-      <c r="K36" s="32"/>
-      <c r="L36" s="35" t="s">
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="M36" s="35"/>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="21" t="s">
+      <c r="N36" s="16"/>
+      <c r="O36" s="16"/>
+      <c r="P36" s="16"/>
+      <c r="Q36" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="Q36" s="21"/>
-    </row>
-    <row r="37" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R36" s="18"/>
+    </row>
+    <row r="37" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="15" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="35" t="s">
+      <c r="E37" s="22"/>
+      <c r="F37" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="G37" s="35"/>
-      <c r="H37" s="35"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="32"/>
-      <c r="K37" s="32"/>
-      <c r="L37" s="40" t="s">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="M37" s="40"/>
-      <c r="N37" s="40"/>
-      <c r="O37" s="40"/>
-      <c r="P37" s="14" t="s">
+      <c r="N37" s="32"/>
+      <c r="O37" s="32"/>
+      <c r="P37" s="32"/>
+      <c r="Q37" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="Q37" s="14"/>
-    </row>
-    <row r="38" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R37" s="21"/>
+    </row>
+    <row r="38" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4"/>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="14" t="s">
+      <c r="C38" s="18"/>
+      <c r="D38" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="E38" s="14"/>
-      <c r="F38" s="20" t="s">
+      <c r="E38" s="21"/>
+      <c r="F38" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="14" t="s">
+      <c r="G38" s="23"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="M38" s="14"/>
-      <c r="N38" s="24" t="s">
+      <c r="N38" s="21"/>
+      <c r="O38" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="O38" s="24"/>
-      <c r="P38" s="24"/>
-      <c r="Q38" s="24"/>
-    </row>
-    <row r="39" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+    </row>
+    <row r="39" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4"/>
-      <c r="B39" s="14" t="s">
+      <c r="B39" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14" t="s">
+      <c r="C39" s="21"/>
+      <c r="D39" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14" t="s">
+      <c r="E39" s="21"/>
+      <c r="F39" s="21" t="s">
         <v>164</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14" t="s">
+      <c r="G39" s="21"/>
+      <c r="H39" s="21" t="s">
         <v>165</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="21" t="s">
+      <c r="I39" s="21"/>
+      <c r="J39" s="21"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="M39" s="21"/>
-      <c r="N39" s="40" t="s">
+      <c r="N39" s="18"/>
+      <c r="O39" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="O39" s="40"/>
-      <c r="P39" s="40"/>
-      <c r="Q39" s="40"/>
-    </row>
-    <row r="40" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="14" t="s">
+      <c r="P39" s="32"/>
+      <c r="Q39" s="32"/>
+      <c r="R39" s="32"/>
+    </row>
+    <row r="40" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14" t="s">
+      <c r="E40" s="21"/>
+      <c r="F40" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="25"/>
-      <c r="I40" s="25"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="32"/>
-      <c r="L40" s="14" t="s">
+      <c r="G40" s="21"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="22" t="s">
+      <c r="N40" s="21"/>
+      <c r="O40" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="O40" s="22"/>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22"/>
-    </row>
-    <row r="41" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="14" t="s">
+      <c r="P40" s="27"/>
+      <c r="Q40" s="27"/>
+      <c r="R40" s="27"/>
+    </row>
+    <row r="41" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="21" t="s">
+      <c r="E41" s="21"/>
+      <c r="F41" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="G41" s="21"/>
-      <c r="H41" s="14" t="s">
+      <c r="G41" s="18"/>
+      <c r="H41" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="23" t="s">
+      <c r="I41" s="21"/>
+      <c r="J41" s="21"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="M41" s="23"/>
-      <c r="N41" s="23"/>
-      <c r="O41" s="23"/>
-      <c r="P41" s="21" t="s">
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="Q41" s="21"/>
-    </row>
-    <row r="42" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R41" s="18"/>
+    </row>
+    <row r="42" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="21" t="s">
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="E42" s="21"/>
-      <c r="F42" s="14" t="s">
+      <c r="E42" s="18"/>
+      <c r="F42" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
+      <c r="G42" s="21"/>
+      <c r="H42" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="32"/>
-      <c r="L42" s="14" t="s">
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="M42" s="14"/>
-      <c r="N42" s="15" t="s">
+      <c r="N42" s="21"/>
+      <c r="O42" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="O42" s="15"/>
-      <c r="P42" s="14" t="s">
+      <c r="P42" s="22"/>
+      <c r="Q42" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="Q42" s="14"/>
-    </row>
-    <row r="43" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R42" s="21"/>
+    </row>
+    <row r="43" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="14" t="s">
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14" t="s">
+      <c r="E43" s="21"/>
+      <c r="F43" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14" t="s">
+      <c r="G43" s="21"/>
+      <c r="H43" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="32"/>
-      <c r="L43" s="15" t="s">
+      <c r="I43" s="21"/>
+      <c r="J43" s="21"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="M43" s="15"/>
-      <c r="N43" s="21" t="s">
+      <c r="N43" s="22"/>
+      <c r="O43" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="O43" s="21"/>
-      <c r="P43" s="21" t="s">
+      <c r="P43" s="18"/>
+      <c r="Q43" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="Q43" s="21"/>
-    </row>
-    <row r="44" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R43" s="18"/>
+    </row>
+    <row r="44" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="14" t="s">
+      <c r="B44" s="20"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="G44" s="14"/>
-      <c r="H44" s="21" t="s">
+      <c r="G44" s="21"/>
+      <c r="H44" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="I44" s="21"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="32"/>
-      <c r="L44" s="14" t="s">
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="M44" s="14"/>
-      <c r="N44" s="21" t="s">
+      <c r="N44" s="21"/>
+      <c r="O44" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="O44" s="21"/>
-      <c r="P44" s="21" t="s">
+      <c r="P44" s="18"/>
+      <c r="Q44" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="Q44" s="21"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A45" s="7">
+      <c r="R44" s="18"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A45" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="38" t="s">
+      <c r="C46" s="14"/>
+      <c r="D46" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="38"/>
-      <c r="L46" s="38"/>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="38"/>
-      <c r="P46" s="38"/>
-      <c r="Q46" s="38"/>
-    </row>
-    <row r="47" spans="1:17" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+      <c r="M46" s="15"/>
+      <c r="N46" s="15"/>
+      <c r="O46" s="15"/>
+      <c r="P46" s="15"/>
+      <c r="Q46" s="15"/>
+      <c r="R46" s="15"/>
+    </row>
+    <row r="47" spans="1:18" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2"/>
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="33" t="s">
+      <c r="C47" s="16"/>
+      <c r="D47" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33" t="s">
+      <c r="E47" s="17"/>
+      <c r="F47" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33" t="s">
+      <c r="G47" s="17"/>
+      <c r="H47" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="I47" s="33"/>
-      <c r="J47" s="21" t="s">
+      <c r="I47" s="17"/>
+      <c r="J47" s="17"/>
+      <c r="K47" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="K47" s="21"/>
-      <c r="L47" s="33" t="s">
+      <c r="L47" s="18"/>
+      <c r="M47" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33" t="s">
+      <c r="N47" s="17"/>
+      <c r="O47" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33" t="s">
+      <c r="P47" s="17"/>
+      <c r="Q47" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="Q47" s="33"/>
-    </row>
-    <row r="48" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
-      <c r="B48" s="25"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="25"/>
-      <c r="E48" s="25"/>
-      <c r="F48" s="14" t="s">
+      <c r="B48" s="20"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14" t="s">
+      <c r="G48" s="21"/>
+      <c r="H48" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="21" t="s">
+      <c r="I48" s="21"/>
+      <c r="J48" s="21"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="19"/>
+      <c r="M48" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="M48" s="21"/>
-      <c r="N48" s="21" t="s">
+      <c r="N48" s="18"/>
+      <c r="O48" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="O48" s="21"/>
-      <c r="P48" s="21" t="s">
+      <c r="P48" s="18"/>
+      <c r="Q48" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="Q48" s="21"/>
-    </row>
-    <row r="49" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R48" s="18"/>
+    </row>
+    <row r="49" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="21" t="s">
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="G49" s="21"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="32"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="25"/>
-      <c r="N49" s="14" t="s">
+      <c r="G49" s="18"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="20"/>
+      <c r="N49" s="20"/>
+      <c r="O49" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="O49" s="14"/>
-      <c r="P49" s="15" t="s">
+      <c r="P49" s="21"/>
+      <c r="Q49" s="22" t="s">
         <v>197</v>
       </c>
-      <c r="Q49" s="15"/>
-    </row>
-    <row r="50" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R49" s="22"/>
+    </row>
+    <row r="50" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
-      <c r="B50" s="25"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="25"/>
-      <c r="E50" s="25"/>
-      <c r="F50" s="25"/>
-      <c r="G50" s="25"/>
-      <c r="H50" s="25"/>
-      <c r="I50" s="25"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="32"/>
-      <c r="L50" s="25"/>
-      <c r="M50" s="25"/>
-      <c r="N50" s="25"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="14" t="s">
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="20"/>
+      <c r="N50" s="20"/>
+      <c r="O50" s="20"/>
+      <c r="P50" s="20"/>
+      <c r="Q50" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="Q50" s="14"/>
-    </row>
-    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="8" t="s">
+      <c r="R50" s="21"/>
+    </row>
+    <row r="51" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B51" s="25"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="25"/>
-      <c r="E51" s="25"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="25"/>
-      <c r="H51" s="25"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="32"/>
-      <c r="L51" s="25"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="25"/>
-      <c r="O51" s="25"/>
-      <c r="P51" s="25"/>
-      <c r="Q51" s="25"/>
-    </row>
-    <row r="52" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="20"/>
+      <c r="G51" s="20"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="20"/>
+      <c r="N51" s="20"/>
+      <c r="O51" s="20"/>
+      <c r="P51" s="20"/>
+      <c r="Q51" s="20"/>
+      <c r="R51" s="20"/>
+    </row>
+    <row r="52" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
-      <c r="B52" s="25"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="14" t="s">
+      <c r="B52" s="20"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="I52" s="14"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="32"/>
-      <c r="L52" s="30"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="21"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
       <c r="M52" s="30"/>
-      <c r="N52" s="31"/>
+      <c r="N52" s="30"/>
       <c r="O52" s="31"/>
-      <c r="P52" s="25"/>
-      <c r="Q52" s="25"/>
-    </row>
-    <row r="53" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P52" s="31"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+    </row>
+    <row r="53" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="31"/>
       <c r="E53" s="31"/>
-      <c r="F53" s="35" t="s">
+      <c r="F53" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="G53" s="35"/>
-      <c r="H53" s="35"/>
-      <c r="I53" s="35"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="32"/>
-      <c r="L53" s="23" t="s">
+      <c r="G53" s="16"/>
+      <c r="H53" s="16"/>
+      <c r="I53" s="16"/>
+      <c r="J53" s="16"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="33" t="s">
         <v>200</v>
       </c>
-      <c r="M53" s="23"/>
-      <c r="N53" s="23"/>
-      <c r="O53" s="23"/>
-      <c r="P53" s="21" t="s">
+      <c r="N53" s="33"/>
+      <c r="O53" s="33"/>
+      <c r="P53" s="33"/>
+      <c r="Q53" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="Q53" s="21"/>
-    </row>
-    <row r="54" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R53" s="18"/>
+    </row>
+    <row r="54" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4"/>
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="20" t="s">
+      <c r="C54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="32"/>
-      <c r="L54" s="14" t="s">
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14" t="s">
+      <c r="N54" s="21"/>
+      <c r="O54" s="21" t="s">
         <v>205</v>
       </c>
-      <c r="O54" s="14"/>
-      <c r="P54" s="14" t="s">
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="Q54" s="14"/>
-    </row>
-    <row r="55" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R54" s="21"/>
+    </row>
+    <row r="55" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4"/>
-      <c r="B55" s="14" t="s">
+      <c r="B55" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="C55" s="14"/>
-      <c r="D55" s="21" t="s">
+      <c r="C55" s="21"/>
+      <c r="D55" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="E55" s="21"/>
-      <c r="F55" s="15" t="s">
+      <c r="E55" s="18"/>
+      <c r="F55" s="22" t="s">
         <v>208</v>
       </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="32"/>
-      <c r="L55" s="14" t="s">
+      <c r="G55" s="22"/>
+      <c r="H55" s="22"/>
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="24"/>
+      <c r="M55" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="M55" s="14"/>
-      <c r="N55" s="19" t="s">
+      <c r="N55" s="21"/>
+      <c r="O55" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
-    </row>
-    <row r="56" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P55" s="25"/>
+      <c r="Q55" s="25"/>
+      <c r="R55" s="25"/>
+    </row>
+    <row r="56" spans="1:18" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4"/>
-      <c r="B56" s="15" t="s">
+      <c r="B56" s="22" t="s">
         <v>211</v>
       </c>
-      <c r="C56" s="15"/>
-      <c r="D56" s="21" t="s">
+      <c r="C56" s="22"/>
+      <c r="D56" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E56" s="21"/>
-      <c r="F56" s="15" t="s">
+      <c r="E56" s="18"/>
+      <c r="F56" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="G56" s="15"/>
-      <c r="H56" s="14" t="s">
+      <c r="G56" s="22"/>
+      <c r="H56" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="32"/>
-      <c r="L56" s="21" t="s">
+      <c r="I56" s="21"/>
+      <c r="J56" s="21"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="24"/>
+      <c r="M56" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="M56" s="21"/>
-      <c r="N56" s="21"/>
-      <c r="O56" s="21"/>
-      <c r="P56" s="21" t="s">
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="18" t="s">
         <v>215</v>
       </c>
-      <c r="Q56" s="21"/>
-    </row>
-    <row r="57" spans="1:17" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R56" s="18"/>
+    </row>
+    <row r="57" spans="1:18" ht="15.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
-      <c r="B57" s="21" t="s">
+      <c r="B57" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="C57" s="21"/>
-      <c r="D57" s="14" t="s">
+      <c r="C57" s="18"/>
+      <c r="D57" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14" t="s">
+      <c r="E57" s="21"/>
+      <c r="F57" s="21" t="s">
         <v>217</v>
       </c>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14" t="s">
+      <c r="G57" s="21"/>
+      <c r="H57" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="I57" s="14"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="32"/>
-      <c r="L57" s="15" t="s">
+      <c r="I57" s="21"/>
+      <c r="J57" s="21"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="24"/>
+      <c r="M57" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="M57" s="15"/>
-      <c r="N57" s="21" t="s">
+      <c r="N57" s="22"/>
+      <c r="O57" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="O57" s="21"/>
-      <c r="P57" s="14" t="s">
+      <c r="P57" s="18"/>
+      <c r="Q57" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="Q57" s="14"/>
-    </row>
-    <row r="58" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="21" t="s">
+      <c r="R57" s="21"/>
+    </row>
+    <row r="58" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="15" t="s">
+      <c r="C58" s="18"/>
+      <c r="D58" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="14" t="s">
+      <c r="E58" s="22"/>
+      <c r="F58" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14" t="s">
+      <c r="G58" s="21"/>
+      <c r="H58" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="I58" s="14"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="32"/>
-      <c r="L58" s="14" t="s">
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="24"/>
+      <c r="M58" s="21" t="s">
         <v>224</v>
       </c>
-      <c r="M58" s="14"/>
-      <c r="N58" s="21" t="s">
+      <c r="N58" s="21"/>
+      <c r="O58" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21" t="s">
+      <c r="P58" s="18"/>
+      <c r="Q58" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="Q58" s="21"/>
-    </row>
-    <row r="59" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R58" s="18"/>
+    </row>
+    <row r="59" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4"/>
-      <c r="B59" s="25"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="14" t="s">
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14" t="s">
+      <c r="E59" s="21"/>
+      <c r="F59" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14" t="s">
+      <c r="G59" s="21"/>
+      <c r="H59" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="I59" s="14"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="14" t="s">
+      <c r="I59" s="21"/>
+      <c r="J59" s="21"/>
+      <c r="K59" s="24"/>
+      <c r="L59" s="24"/>
+      <c r="M59" s="21" t="s">
         <v>229</v>
       </c>
-      <c r="M59" s="14"/>
-      <c r="N59" s="21" t="s">
+      <c r="N59" s="21"/>
+      <c r="O59" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="O59" s="21"/>
-      <c r="P59" s="21" t="s">
+      <c r="P59" s="18"/>
+      <c r="Q59" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="Q59" s="21"/>
-    </row>
-    <row r="60" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R59" s="18"/>
+    </row>
+    <row r="60" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4"/>
-      <c r="B60" s="21" t="s">
+      <c r="B60" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="C60" s="21"/>
-      <c r="D60" s="14" t="s">
+      <c r="C60" s="18"/>
+      <c r="D60" s="21" t="s">
         <v>232</v>
       </c>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14" t="s">
+      <c r="E60" s="21"/>
+      <c r="F60" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14" t="s">
+      <c r="G60" s="21"/>
+      <c r="H60" s="21" t="s">
         <v>233</v>
       </c>
-      <c r="I60" s="14"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="32"/>
-      <c r="L60" s="14" t="s">
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="24"/>
+      <c r="L60" s="24"/>
+      <c r="M60" s="21" t="s">
         <v>234</v>
       </c>
-      <c r="M60" s="14"/>
-      <c r="N60" s="21" t="s">
+      <c r="N60" s="21"/>
+      <c r="O60" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="O60" s="21"/>
-      <c r="P60" s="21" t="s">
+      <c r="P60" s="18"/>
+      <c r="Q60" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="Q60" s="21"/>
-    </row>
-    <row r="61" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R60" s="18"/>
+    </row>
+    <row r="61" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="14" t="s">
+      <c r="B61" s="20"/>
+      <c r="C61" s="20"/>
+      <c r="D61" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14" t="s">
+      <c r="E61" s="21"/>
+      <c r="F61" s="21" t="s">
         <v>238</v>
       </c>
-      <c r="G61" s="14"/>
-      <c r="H61" s="21" t="s">
+      <c r="G61" s="21"/>
+      <c r="H61" s="18" t="s">
         <v>239</v>
       </c>
-      <c r="I61" s="21"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="32"/>
-      <c r="L61" s="21" t="s">
+      <c r="I61" s="18"/>
+      <c r="J61" s="18"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="24"/>
+      <c r="M61" s="18" t="s">
         <v>240</v>
       </c>
-      <c r="M61" s="21"/>
-      <c r="N61" s="21" t="s">
+      <c r="N61" s="18"/>
+      <c r="O61" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="O61" s="21"/>
-      <c r="P61" s="21" t="s">
+      <c r="P61" s="18"/>
+      <c r="Q61" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="Q61" s="21"/>
-    </row>
-    <row r="62" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R61" s="18"/>
+    </row>
+    <row r="62" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4"/>
-      <c r="B62" s="25"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="14" t="s">
+      <c r="B62" s="20"/>
+      <c r="C62" s="20"/>
+      <c r="D62" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="21" t="s">
+      <c r="E62" s="21"/>
+      <c r="F62" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21" t="s">
+      <c r="G62" s="18"/>
+      <c r="H62" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="I62" s="21"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="32"/>
-      <c r="L62" s="14" t="s">
+      <c r="I62" s="18"/>
+      <c r="J62" s="18"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="24"/>
+      <c r="M62" s="21" t="s">
         <v>246</v>
       </c>
-      <c r="M62" s="14"/>
-      <c r="N62" s="25"/>
-      <c r="O62" s="25"/>
-      <c r="P62" s="14" t="s">
+      <c r="N62" s="21"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="Q62" s="14"/>
-    </row>
-    <row r="63" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R62" s="21"/>
+    </row>
+    <row r="63" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4"/>
-      <c r="B63" s="25"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="32"/>
-      <c r="L63" s="25"/>
-      <c r="M63" s="25"/>
-      <c r="N63" s="25"/>
-      <c r="O63" s="25"/>
-      <c r="P63" s="14" t="s">
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="24"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
+      <c r="P63" s="20"/>
+      <c r="Q63" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="Q63" s="14"/>
-    </row>
-    <row r="64" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R63" s="21"/>
+    </row>
+    <row r="64" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4"/>
-      <c r="B64" s="25"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="25"/>
-      <c r="E64" s="25"/>
-      <c r="F64" s="21" t="s">
+      <c r="B64" s="20"/>
+      <c r="C64" s="20"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="G64" s="21"/>
-      <c r="H64" s="25"/>
-      <c r="I64" s="25"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="32"/>
-      <c r="L64" s="25"/>
-      <c r="M64" s="25"/>
-      <c r="N64" s="25"/>
-      <c r="O64" s="25"/>
-      <c r="P64" s="14" t="s">
+      <c r="G64" s="18"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="24"/>
+      <c r="M64" s="20"/>
+      <c r="N64" s="20"/>
+      <c r="O64" s="20"/>
+      <c r="P64" s="20"/>
+      <c r="Q64" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="Q64" s="14"/>
-    </row>
-    <row r="65" spans="1:17" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R64" s="21"/>
+    </row>
+    <row r="65" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
-      <c r="B65" s="25"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="25"/>
-      <c r="E65" s="25"/>
-      <c r="F65" s="25"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="25"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="32"/>
-      <c r="L65" s="25"/>
-      <c r="M65" s="25"/>
-      <c r="N65" s="25"/>
-      <c r="O65" s="25"/>
-      <c r="P65" s="25"/>
-      <c r="Q65" s="25"/>
-    </row>
-    <row r="66" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="H65" s="20"/>
+      <c r="I65" s="20"/>
+      <c r="J65" s="20"/>
+      <c r="K65" s="24"/>
+      <c r="L65" s="24"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
+      <c r="P65" s="20"/>
+      <c r="Q65" s="20"/>
+      <c r="R65" s="20"/>
+    </row>
+    <row r="66" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="34" t="s">
         <v>271</v>
       </c>
-      <c r="B66" s="25"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="25"/>
-      <c r="E66" s="25"/>
-      <c r="F66" s="25"/>
-      <c r="G66" s="25"/>
-      <c r="H66" s="25"/>
-      <c r="I66" s="25"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="32"/>
-      <c r="L66" s="25"/>
-      <c r="M66" s="25"/>
-      <c r="N66" s="25"/>
-      <c r="O66" s="25"/>
-      <c r="P66" s="25"/>
-      <c r="Q66" s="25"/>
-    </row>
-    <row r="67" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="20"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+      <c r="K66" s="24"/>
+      <c r="L66" s="24"/>
+      <c r="M66" s="20"/>
+      <c r="N66" s="20"/>
+      <c r="O66" s="20"/>
+      <c r="P66" s="20"/>
+      <c r="Q66" s="20"/>
+      <c r="R66" s="20"/>
+    </row>
+    <row r="67" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="34"/>
-      <c r="B67" s="25"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="14" t="s">
+      <c r="B67" s="20"/>
+      <c r="C67" s="20"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="I67" s="14"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="32"/>
-      <c r="L67" s="25"/>
-      <c r="M67" s="25"/>
-      <c r="N67" s="25"/>
-      <c r="O67" s="25"/>
-      <c r="P67" s="21" t="s">
+      <c r="I67" s="21"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="24"/>
+      <c r="L67" s="24"/>
+      <c r="M67" s="20"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="20"/>
+      <c r="P67" s="20"/>
+      <c r="Q67" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="Q67" s="21"/>
-    </row>
-    <row r="68" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R67" s="18"/>
+    </row>
+    <row r="68" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="15" t="s">
+      <c r="B68" s="20"/>
+      <c r="C68" s="20"/>
+      <c r="D68" s="22" t="s">
         <v>251</v>
       </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="33" t="s">
+      <c r="E68" s="22"/>
+      <c r="F68" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="G68" s="33"/>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="32"/>
-      <c r="L68" s="14" t="s">
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="24"/>
+      <c r="M68" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="M68" s="14"/>
-      <c r="N68" s="14" t="s">
+      <c r="N68" s="21"/>
+      <c r="O68" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="O68" s="14"/>
-      <c r="P68" s="21" t="s">
+      <c r="P68" s="21"/>
+      <c r="Q68" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="Q68" s="21"/>
-    </row>
-    <row r="69" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R68" s="18"/>
+    </row>
+    <row r="69" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C69" s="24"/>
-      <c r="D69" s="24"/>
-      <c r="E69" s="24"/>
-      <c r="F69" s="24" t="s">
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26" t="s">
         <v>255</v>
       </c>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="32"/>
-      <c r="L69" s="35" t="s">
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="24"/>
+      <c r="M69" s="16" t="s">
         <v>256</v>
       </c>
-      <c r="M69" s="35"/>
-      <c r="N69" s="35"/>
-      <c r="O69" s="35"/>
-      <c r="P69" s="14" t="s">
+      <c r="N69" s="16"/>
+      <c r="O69" s="16"/>
+      <c r="P69" s="16"/>
+      <c r="Q69" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="Q69" s="14"/>
-    </row>
-    <row r="70" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R69" s="21"/>
+    </row>
+    <row r="70" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4"/>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="16" t="s">
         <v>257</v>
       </c>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="21" t="s">
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="21"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="32"/>
-      <c r="L70" s="24" t="s">
+      <c r="G70" s="18"/>
+      <c r="H70" s="18"/>
+      <c r="I70" s="18"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="24"/>
+      <c r="L70" s="24"/>
+      <c r="M70" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="M70" s="24"/>
-      <c r="N70" s="24"/>
-      <c r="O70" s="24"/>
-      <c r="P70" s="14" t="s">
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="21" t="s">
         <v>260</v>
       </c>
-      <c r="Q70" s="14"/>
-    </row>
-    <row r="71" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R70" s="21"/>
+    </row>
+    <row r="71" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4"/>
-      <c r="B71" s="21" t="s">
+      <c r="B71" s="18" t="s">
         <v>261</v>
       </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="14" t="s">
+      <c r="C71" s="18"/>
+      <c r="D71" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="E71" s="14"/>
-      <c r="F71" s="19" t="s">
+      <c r="E71" s="21"/>
+      <c r="F71" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="19"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="32"/>
-      <c r="L71" s="24" t="s">
+      <c r="G71" s="25"/>
+      <c r="H71" s="25"/>
+      <c r="I71" s="25"/>
+      <c r="J71" s="25"/>
+      <c r="K71" s="24"/>
+      <c r="L71" s="24"/>
+      <c r="M71" s="26" t="s">
         <v>264</v>
       </c>
-      <c r="M71" s="24"/>
-      <c r="N71" s="24"/>
-      <c r="O71" s="24"/>
-      <c r="P71" s="14" t="s">
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="Q71" s="14"/>
-    </row>
-    <row r="72" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R71" s="21"/>
+    </row>
+    <row r="72" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4"/>
-      <c r="B72" s="21" t="s">
+      <c r="B72" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="C72" s="21"/>
-      <c r="D72" s="14" t="s">
+      <c r="C72" s="18"/>
+      <c r="D72" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="E72" s="14"/>
-      <c r="F72" s="23" t="s">
+      <c r="E72" s="21"/>
+      <c r="F72" s="33" t="s">
         <v>267</v>
       </c>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="32"/>
-      <c r="L72" s="14" t="s">
+      <c r="G72" s="33"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="33"/>
+      <c r="J72" s="33"/>
+      <c r="K72" s="24"/>
+      <c r="L72" s="24"/>
+      <c r="M72" s="21" t="s">
         <v>268</v>
       </c>
-      <c r="M72" s="14"/>
-      <c r="N72" s="21" t="s">
+      <c r="N72" s="21"/>
+      <c r="O72" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="O72" s="21"/>
-      <c r="P72" s="14" t="s">
+      <c r="P72" s="18"/>
+      <c r="Q72" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="Q72" s="14"/>
-    </row>
-    <row r="73" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="21" t="s">
+      <c r="R72" s="21"/>
+    </row>
+    <row r="73" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B73" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="C73" s="21"/>
-      <c r="D73" s="14" t="s">
+      <c r="C73" s="18"/>
+      <c r="D73" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="E73" s="14"/>
-      <c r="F73" s="22" t="s">
+      <c r="E73" s="21"/>
+      <c r="F73" s="27" t="s">
         <v>274</v>
       </c>
-      <c r="G73" s="22"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="32"/>
-      <c r="L73" s="14" t="s">
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
+      <c r="K73" s="24"/>
+      <c r="L73" s="24"/>
+      <c r="M73" s="21" t="s">
         <v>275</v>
       </c>
-      <c r="M73" s="14"/>
-      <c r="N73" s="21" t="s">
+      <c r="N73" s="21"/>
+      <c r="O73" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="O73" s="21"/>
-      <c r="P73" s="14" t="s">
+      <c r="P73" s="18"/>
+      <c r="Q73" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="Q73" s="14"/>
-    </row>
-    <row r="74" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B74" s="21" t="s">
+      <c r="R73" s="21"/>
+    </row>
+    <row r="74" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B74" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="C74" s="21"/>
-      <c r="D74" s="14" t="s">
+      <c r="C74" s="18"/>
+      <c r="D74" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E74" s="14"/>
-      <c r="F74" s="21" t="s">
+      <c r="E74" s="21"/>
+      <c r="F74" s="18" t="s">
         <v>278</v>
       </c>
-      <c r="G74" s="21"/>
-      <c r="H74" s="14" t="s">
+      <c r="G74" s="18"/>
+      <c r="H74" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="I74" s="14"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="32"/>
-      <c r="L74" s="14" t="s">
+      <c r="I74" s="21"/>
+      <c r="J74" s="21"/>
+      <c r="K74" s="24"/>
+      <c r="L74" s="24"/>
+      <c r="M74" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="M74" s="14"/>
-      <c r="N74" s="21" t="s">
+      <c r="N74" s="21"/>
+      <c r="O74" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="O74" s="21"/>
-      <c r="P74" s="14" t="s">
+      <c r="P74" s="18"/>
+      <c r="Q74" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="Q74" s="14"/>
-    </row>
-    <row r="75" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R74" s="21"/>
+    </row>
+    <row r="75" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4"/>
-      <c r="B75" s="25"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="14" t="s">
+      <c r="B75" s="20"/>
+      <c r="C75" s="20"/>
+      <c r="D75" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="E75" s="14"/>
-      <c r="F75" s="15" t="s">
+      <c r="E75" s="21"/>
+      <c r="F75" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="G75" s="15"/>
-      <c r="H75" s="14" t="s">
+      <c r="G75" s="22"/>
+      <c r="H75" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="I75" s="14"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="32"/>
-      <c r="L75" s="21" t="s">
+      <c r="I75" s="21"/>
+      <c r="J75" s="21"/>
+      <c r="K75" s="24"/>
+      <c r="L75" s="24"/>
+      <c r="M75" s="18" t="s">
         <v>283</v>
       </c>
-      <c r="M75" s="21"/>
-      <c r="N75" s="33" t="s">
+      <c r="N75" s="18"/>
+      <c r="O75" s="17" t="s">
         <v>284</v>
       </c>
-      <c r="O75" s="33"/>
-      <c r="P75" s="21" t="s">
+      <c r="P75" s="17"/>
+      <c r="Q75" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="Q75" s="21"/>
-    </row>
-    <row r="76" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R75" s="18"/>
+    </row>
+    <row r="76" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="14" t="s">
+      <c r="B76" s="20"/>
+      <c r="C76" s="20"/>
+      <c r="D76" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14" t="s">
+      <c r="E76" s="21"/>
+      <c r="F76" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14" t="s">
+      <c r="G76" s="21"/>
+      <c r="H76" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="32"/>
-      <c r="L76" s="15" t="s">
+      <c r="I76" s="21"/>
+      <c r="J76" s="21"/>
+      <c r="K76" s="24"/>
+      <c r="L76" s="24"/>
+      <c r="M76" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="M76" s="15"/>
-      <c r="N76" s="14" t="s">
+      <c r="N76" s="22"/>
+      <c r="O76" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="O76" s="14"/>
-      <c r="P76" s="14" t="s">
+      <c r="P76" s="21"/>
+      <c r="Q76" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="Q76" s="14"/>
-    </row>
-    <row r="77" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R76" s="21"/>
+    </row>
+    <row r="77" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
-      <c r="B77" s="25"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="21" t="s">
+      <c r="B77" s="20"/>
+      <c r="C77" s="20"/>
+      <c r="D77" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="E77" s="21"/>
-      <c r="F77" s="15" t="s">
+      <c r="E77" s="18"/>
+      <c r="F77" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15" t="s">
+      <c r="G77" s="22"/>
+      <c r="H77" s="22" t="s">
         <v>222</v>
       </c>
-      <c r="I77" s="15"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="15" t="s">
+      <c r="I77" s="22"/>
+      <c r="J77" s="22"/>
+      <c r="K77" s="24"/>
+      <c r="L77" s="24"/>
+      <c r="M77" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="M77" s="15"/>
-      <c r="N77" s="15" t="s">
+      <c r="N77" s="22"/>
+      <c r="O77" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="O77" s="15"/>
-      <c r="P77" s="21" t="s">
+      <c r="P77" s="22"/>
+      <c r="Q77" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="Q77" s="21"/>
-    </row>
-    <row r="78" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R77" s="18"/>
+    </row>
+    <row r="78" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4"/>
-      <c r="B78" s="25"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="21" t="s">
+      <c r="B78" s="20"/>
+      <c r="C78" s="20"/>
+      <c r="D78" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="E78" s="21"/>
-      <c r="F78" s="14" t="s">
+      <c r="E78" s="18"/>
+      <c r="F78" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="G78" s="14"/>
-      <c r="H78" s="21" t="s">
+      <c r="G78" s="21"/>
+      <c r="H78" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="I78" s="21"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="32"/>
-      <c r="L78" s="15" t="s">
+      <c r="I78" s="18"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="24"/>
+      <c r="L78" s="24"/>
+      <c r="M78" s="22" t="s">
         <v>299</v>
       </c>
-      <c r="M78" s="15"/>
-      <c r="N78" s="21" t="s">
+      <c r="N78" s="22"/>
+      <c r="O78" s="18" t="s">
         <v>300</v>
       </c>
-      <c r="O78" s="21"/>
-      <c r="P78" s="25"/>
-      <c r="Q78" s="25"/>
-    </row>
-    <row r="79" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P78" s="18"/>
+      <c r="Q78" s="20"/>
+      <c r="R78" s="20"/>
+    </row>
+    <row r="79" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4"/>
-      <c r="B79" s="25"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="25"/>
-      <c r="E79" s="25"/>
-      <c r="F79" s="25"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="14" t="s">
+      <c r="B79" s="20"/>
+      <c r="C79" s="20"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="20"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="I79" s="14"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="32"/>
-      <c r="L79" s="14" t="s">
+      <c r="I79" s="21"/>
+      <c r="J79" s="21"/>
+      <c r="K79" s="24"/>
+      <c r="L79" s="24"/>
+      <c r="M79" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="M79" s="14"/>
-      <c r="N79" s="21" t="s">
+      <c r="N79" s="21"/>
+      <c r="O79" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="O79" s="21"/>
-      <c r="P79" s="25"/>
-      <c r="Q79" s="25"/>
-    </row>
-    <row r="80" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="P79" s="18"/>
+      <c r="Q79" s="20"/>
+      <c r="R79" s="20"/>
+    </row>
+    <row r="80" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="25"/>
-      <c r="E80" s="25"/>
-      <c r="F80" s="25"/>
-      <c r="G80" s="25"/>
-      <c r="H80" s="15" t="s">
+      <c r="B80" s="20"/>
+      <c r="C80" s="20"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="I80" s="15"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="32"/>
-      <c r="L80" s="25"/>
-      <c r="M80" s="25"/>
-      <c r="N80" s="25"/>
-      <c r="O80" s="25"/>
-      <c r="P80" s="25"/>
-      <c r="Q80" s="25"/>
-    </row>
-    <row r="81" spans="1:17" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I80" s="22"/>
+      <c r="J80" s="22"/>
+      <c r="K80" s="24"/>
+      <c r="L80" s="24"/>
+      <c r="M80" s="20"/>
+      <c r="N80" s="20"/>
+      <c r="O80" s="20"/>
+      <c r="P80" s="20"/>
+      <c r="Q80" s="20"/>
+      <c r="R80" s="20"/>
+    </row>
+    <row r="81" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="25"/>
-      <c r="E81" s="25"/>
-      <c r="F81" s="25"/>
-      <c r="G81" s="25"/>
-      <c r="H81" s="25"/>
-      <c r="I81" s="25"/>
-      <c r="J81" s="26"/>
-      <c r="K81" s="26"/>
-      <c r="L81" s="25"/>
-      <c r="M81" s="25"/>
-      <c r="N81" s="25"/>
-      <c r="O81" s="25"/>
-      <c r="P81" s="25"/>
-      <c r="Q81" s="25"/>
-    </row>
-    <row r="82" spans="1:17" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B81" s="20"/>
+      <c r="C81" s="20"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="35"/>
+      <c r="L81" s="35"/>
+      <c r="M81" s="20"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+    </row>
+    <row r="82" spans="1:18" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B82" s="25"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="25"/>
-      <c r="E82" s="25"/>
-      <c r="F82" s="25"/>
-      <c r="G82" s="25"/>
-      <c r="H82" s="25"/>
-      <c r="I82" s="25"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="28"/>
-      <c r="M82" s="28"/>
-      <c r="N82" s="28"/>
-      <c r="O82" s="28"/>
-      <c r="P82" s="29"/>
-      <c r="Q82" s="29"/>
-    </row>
-    <row r="83" spans="1:17" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="20"/>
+      <c r="C82" s="20"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="36"/>
+      <c r="L82" s="36"/>
+      <c r="M82" s="37"/>
+      <c r="N82" s="37"/>
+      <c r="O82" s="37"/>
+      <c r="P82" s="37"/>
+      <c r="Q82" s="38"/>
+      <c r="R82" s="38"/>
+    </row>
+    <row r="83" spans="1:18" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="30"/>
       <c r="C83" s="30"/>
       <c r="D83" s="31"/>
       <c r="E83" s="31"/>
-      <c r="F83" s="22" t="s">
+      <c r="F83" s="27" t="s">
         <v>304</v>
       </c>
-      <c r="G83" s="22"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="22"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
       <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
-      <c r="L83" s="28"/>
-      <c r="M83" s="28"/>
-      <c r="N83" s="28"/>
-      <c r="O83" s="28"/>
-      <c r="P83" s="29"/>
-      <c r="Q83" s="29"/>
-    </row>
-    <row r="84" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K83" s="36"/>
+      <c r="L83" s="36"/>
+      <c r="M83" s="37"/>
+      <c r="N83" s="37"/>
+      <c r="O83" s="37"/>
+      <c r="P83" s="37"/>
+      <c r="Q83" s="38"/>
+      <c r="R83" s="38"/>
+    </row>
+    <row r="84" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4"/>
-      <c r="B84" s="23" t="s">
+      <c r="B84" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="C84" s="23"/>
-      <c r="D84" s="23"/>
-      <c r="E84" s="23"/>
-      <c r="F84" s="24" t="s">
+      <c r="C84" s="33"/>
+      <c r="D84" s="33"/>
+      <c r="E84" s="33"/>
+      <c r="F84" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="G84" s="24"/>
-      <c r="H84" s="24"/>
-      <c r="I84" s="24"/>
-      <c r="J84" s="16"/>
-      <c r="K84" s="16"/>
-      <c r="L84" s="17"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="P84" s="18"/>
-      <c r="Q84" s="18"/>
-    </row>
-    <row r="85" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="39"/>
+      <c r="L84" s="39"/>
+      <c r="M84" s="40"/>
+      <c r="N84" s="40"/>
+      <c r="O84" s="40"/>
+      <c r="P84" s="40"/>
+      <c r="Q84" s="41"/>
+      <c r="R84" s="41"/>
+    </row>
+    <row r="85" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
-      <c r="B85" s="20" t="s">
+      <c r="B85" s="23" t="s">
         <v>307</v>
       </c>
-      <c r="C85" s="20"/>
-      <c r="D85" s="20"/>
-      <c r="E85" s="20"/>
-      <c r="F85" s="19" t="s">
+      <c r="C85" s="23"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="19"/>
-      <c r="J85" s="16"/>
-      <c r="K85" s="16"/>
-      <c r="L85" s="17"/>
-      <c r="M85" s="17"/>
-      <c r="N85" s="17"/>
-      <c r="O85" s="17"/>
-      <c r="P85" s="18"/>
-      <c r="Q85" s="18"/>
-    </row>
-    <row r="86" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="25"/>
+      <c r="H85" s="25"/>
+      <c r="I85" s="25"/>
+      <c r="J85" s="25"/>
+      <c r="K85" s="39"/>
+      <c r="L85" s="39"/>
+      <c r="M85" s="40"/>
+      <c r="N85" s="40"/>
+      <c r="O85" s="40"/>
+      <c r="P85" s="40"/>
+      <c r="Q85" s="41"/>
+      <c r="R85" s="41"/>
+    </row>
+    <row r="86" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4"/>
-      <c r="B86" s="19" t="s">
+      <c r="B86" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="20" t="s">
+      <c r="C86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="25"/>
+      <c r="F86" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="16"/>
-      <c r="K86" s="16"/>
-      <c r="L86" s="17"/>
-      <c r="M86" s="17"/>
-      <c r="N86" s="17"/>
-      <c r="O86" s="17"/>
-      <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
-    </row>
-    <row r="87" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="23"/>
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
+      <c r="J86" s="23"/>
+      <c r="K86" s="39"/>
+      <c r="L86" s="39"/>
+      <c r="M86" s="40"/>
+      <c r="N86" s="40"/>
+      <c r="O86" s="40"/>
+      <c r="P86" s="40"/>
+      <c r="Q86" s="41"/>
+      <c r="R86" s="41"/>
+    </row>
+    <row r="87" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="4"/>
-      <c r="B87" s="21" t="s">
+      <c r="B87" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="C87" s="21"/>
-      <c r="D87" s="21" t="s">
+      <c r="C87" s="18"/>
+      <c r="D87" s="18" t="s">
         <v>228</v>
       </c>
-      <c r="E87" s="21"/>
-      <c r="F87" s="22" t="s">
+      <c r="E87" s="18"/>
+      <c r="F87" s="27" t="s">
         <v>312</v>
       </c>
-      <c r="G87" s="22"/>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="16"/>
-      <c r="K87" s="16"/>
-      <c r="L87" s="17"/>
-      <c r="M87" s="17"/>
-      <c r="N87" s="17"/>
-      <c r="O87" s="17"/>
-      <c r="P87" s="18"/>
-      <c r="Q87" s="18"/>
-    </row>
-    <row r="88" spans="1:17" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="27"/>
+      <c r="J87" s="27"/>
+      <c r="K87" s="39"/>
+      <c r="L87" s="39"/>
+      <c r="M87" s="40"/>
+      <c r="N87" s="40"/>
+      <c r="O87" s="40"/>
+      <c r="P87" s="40"/>
+      <c r="Q87" s="41"/>
+      <c r="R87" s="41"/>
+    </row>
+    <row r="88" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="4"/>
-      <c r="B88" s="14" t="s">
+      <c r="B88" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14" t="s">
+      <c r="C88" s="21"/>
+      <c r="D88" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14" t="s">
+      <c r="E88" s="21"/>
+      <c r="F88" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="G88" s="14"/>
-      <c r="H88" s="15" t="s">
+      <c r="G88" s="21"/>
+      <c r="H88" s="22" t="s">
         <v>314</v>
       </c>
-      <c r="I88" s="15"/>
-      <c r="J88" s="16"/>
-      <c r="K88" s="16"/>
-      <c r="L88" s="17"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17"/>
-      <c r="O88" s="17"/>
-      <c r="P88" s="18"/>
-      <c r="Q88" s="18"/>
-    </row>
-    <row r="89" spans="1:17" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B89" s="14" t="s">
+      <c r="I88" s="22"/>
+      <c r="J88" s="22"/>
+      <c r="K88" s="39"/>
+      <c r="L88" s="39"/>
+      <c r="M88" s="40"/>
+      <c r="N88" s="40"/>
+      <c r="O88" s="40"/>
+      <c r="P88" s="40"/>
+      <c r="Q88" s="41"/>
+      <c r="R88" s="41"/>
+    </row>
+    <row r="89" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="C89" s="14"/>
-      <c r="D89" s="14" t="s">
+      <c r="C89" s="21"/>
+      <c r="D89" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14" t="s">
+      <c r="E89" s="21"/>
+      <c r="F89" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14" t="s">
+      <c r="G89" s="21"/>
+      <c r="H89" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="I89" s="14"/>
-      <c r="J89" s="16"/>
-      <c r="K89" s="16"/>
-      <c r="L89" s="17"/>
-      <c r="M89" s="17"/>
-      <c r="N89" s="17"/>
-      <c r="O89" s="17"/>
-      <c r="P89" s="18"/>
-      <c r="Q89" s="18"/>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A90" s="7"/>
-      <c r="C90" s="9"/>
-      <c r="E90" s="10"/>
-      <c r="G90" s="12" t="s">
+      <c r="I89" s="21"/>
+      <c r="J89" s="21"/>
+      <c r="K89" s="39"/>
+      <c r="L89" s="39"/>
+      <c r="M89" s="40"/>
+      <c r="N89" s="40"/>
+      <c r="O89" s="40"/>
+      <c r="P89" s="40"/>
+      <c r="Q89" s="41"/>
+      <c r="R89" s="41"/>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A90" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="32.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1"/>
+      <c r="B91" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" s="14"/>
+      <c r="D91" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E91" s="15"/>
+      <c r="F91" s="15"/>
+      <c r="G91" s="15"/>
+      <c r="H91" s="15"/>
+      <c r="I91" s="15"/>
+      <c r="J91" s="15"/>
+      <c r="K91" s="15"/>
+      <c r="L91" s="15"/>
+      <c r="M91" s="15"/>
+      <c r="N91" s="15"/>
+      <c r="O91" s="15"/>
+      <c r="P91" s="15"/>
+      <c r="Q91" s="15"/>
+      <c r="R91" s="15"/>
+    </row>
+    <row r="92" spans="1:18" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2"/>
+      <c r="B92" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="16"/>
+      <c r="D92" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G92" s="17"/>
+      <c r="H92" s="30"/>
+      <c r="I92" s="30"/>
+      <c r="J92" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K92" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="L92" s="18"/>
+      <c r="M92" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="N92" s="17"/>
+      <c r="O92" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="P92" s="17"/>
+      <c r="Q92" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="R92" s="17"/>
+    </row>
+    <row r="93" spans="1:18" ht="11.85" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3"/>
+      <c r="B93" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" s="18"/>
+      <c r="D93" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E93" s="21"/>
+      <c r="F93" s="21" t="s">
         <v>282</v>
       </c>
-      <c r="I90" s="14" t="s">
+      <c r="G93" s="21"/>
+      <c r="H93" s="21" t="s">
         <v>321</v>
       </c>
-      <c r="J90" s="14"/>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C91" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="E91" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="G91" s="12" t="s">
+      <c r="I93" s="21"/>
+      <c r="J93" s="21"/>
+      <c r="K93" s="36"/>
+      <c r="L93" s="36"/>
+      <c r="M93" s="37"/>
+      <c r="N93" s="37"/>
+      <c r="O93" s="37"/>
+      <c r="P93" s="37"/>
+      <c r="Q93" s="38"/>
+      <c r="R93" s="38"/>
+    </row>
+    <row r="94" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="4"/>
+      <c r="B94" s="18" t="s">
+        <v>261</v>
+      </c>
+      <c r="C94" s="18"/>
+      <c r="D94" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="I91" s="15" t="s">
+      <c r="G94" s="21"/>
+      <c r="H94" s="22" t="s">
         <v>324</v>
       </c>
-      <c r="J91" s="15"/>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C92" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="E92" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G92" s="12" t="s">
+      <c r="I94" s="22"/>
+      <c r="J94" s="22"/>
+      <c r="K94" s="39"/>
+      <c r="L94" s="39"/>
+      <c r="M94" s="40"/>
+      <c r="N94" s="40"/>
+      <c r="O94" s="40"/>
+      <c r="P94" s="40"/>
+      <c r="Q94" s="41"/>
+      <c r="R94" s="41"/>
+    </row>
+    <row r="95" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="4"/>
+      <c r="B95" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="C95" s="18"/>
+      <c r="D95" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E95" s="21"/>
+      <c r="F95" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="I92" s="14" t="s">
+      <c r="G95" s="21"/>
+      <c r="H95" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="J92" s="14"/>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C93" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="E93" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G93" s="12" t="s">
+      <c r="I95" s="21"/>
+      <c r="J95" s="21"/>
+      <c r="K95" s="39"/>
+      <c r="L95" s="39"/>
+      <c r="M95" s="40"/>
+      <c r="N95" s="40"/>
+      <c r="O95" s="40"/>
+      <c r="P95" s="40"/>
+      <c r="Q95" s="41"/>
+      <c r="R95" s="41"/>
+    </row>
+    <row r="96" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="4"/>
+      <c r="B96" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="C96" s="18"/>
+      <c r="D96" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="E96" s="21"/>
+      <c r="F96" s="21" t="s">
         <v>330</v>
       </c>
-      <c r="I93" s="1"/>
-      <c r="J93" s="13"/>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C94" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="E94" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G94" s="12" t="s">
+      <c r="G96" s="21"/>
+      <c r="H96" s="30"/>
+      <c r="I96" s="30"/>
+      <c r="J96" s="7"/>
+      <c r="K96" s="39"/>
+      <c r="L96" s="39"/>
+      <c r="M96" s="40"/>
+      <c r="N96" s="40"/>
+      <c r="O96" s="40"/>
+      <c r="P96" s="40"/>
+      <c r="Q96" s="41"/>
+      <c r="R96" s="41"/>
+    </row>
+    <row r="97" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4"/>
+      <c r="B97" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C97" s="18"/>
+      <c r="D97" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="E97" s="18"/>
+      <c r="F97" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="I94" s="14" t="s">
+      <c r="G97" s="21"/>
+      <c r="H97" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="J94" s="14"/>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C95" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E95" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G95" s="11" t="s">
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="39"/>
+      <c r="L97" s="39"/>
+      <c r="M97" s="40"/>
+      <c r="N97" s="40"/>
+      <c r="O97" s="40"/>
+      <c r="P97" s="40"/>
+      <c r="Q97" s="41"/>
+      <c r="R97" s="41"/>
+    </row>
+    <row r="98" spans="1:18" ht="11.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4"/>
+      <c r="B98" s="20"/>
+      <c r="C98" s="20"/>
+      <c r="D98" s="20"/>
+      <c r="E98" s="20"/>
+      <c r="F98" s="18" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="C96" s="2"/>
-      <c r="G96" s="11" t="s">
+      <c r="G98" s="18"/>
+      <c r="H98" s="30"/>
+      <c r="I98" s="30"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="39"/>
+      <c r="L98" s="39"/>
+      <c r="M98" s="40"/>
+      <c r="N98" s="40"/>
+      <c r="O98" s="40"/>
+      <c r="P98" s="40"/>
+      <c r="Q98" s="41"/>
+      <c r="R98" s="41"/>
+    </row>
+    <row r="99" spans="1:18" ht="10.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="6"/>
+      <c r="B99" s="20"/>
+      <c r="C99" s="20"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="20"/>
+      <c r="F99" s="18" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C97" s="2"/>
+      <c r="G99" s="18"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="7"/>
+      <c r="K99" s="42"/>
+      <c r="L99" s="42"/>
+      <c r="M99" s="43"/>
+      <c r="N99" s="43"/>
+      <c r="O99" s="43"/>
+      <c r="P99" s="43"/>
+      <c r="Q99" s="44"/>
+      <c r="R99" s="44"/>
+    </row>
+    <row r="100" spans="1:18" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3"/>
+      <c r="B100" s="45" t="s">
+        <v>336</v>
+      </c>
+      <c r="C100" s="45"/>
+      <c r="D100" s="46" t="s">
+        <v>337</v>
+      </c>
+      <c r="E100" s="46"/>
+      <c r="F100" s="47" t="s">
+        <v>336</v>
+      </c>
+      <c r="G100" s="47"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="K100" s="36"/>
+      <c r="L100" s="36"/>
+      <c r="M100" s="38"/>
+      <c r="N100" s="38"/>
+      <c r="O100" s="48" t="s">
+        <v>338</v>
+      </c>
+      <c r="P100" s="48"/>
+      <c r="Q100" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="R100" s="45"/>
+    </row>
+    <row r="101" spans="1:18" ht="7.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="4"/>
+      <c r="B101" s="19"/>
+      <c r="C101" s="19"/>
+      <c r="D101" s="19"/>
+      <c r="E101" s="19"/>
+      <c r="F101" s="19"/>
+      <c r="G101" s="19"/>
+      <c r="H101" s="36"/>
+      <c r="I101" s="36"/>
+      <c r="J101" s="10"/>
+      <c r="K101" s="39"/>
+      <c r="L101" s="39"/>
+      <c r="M101" s="41"/>
+      <c r="N101" s="41"/>
+      <c r="O101" s="49" t="s">
+        <v>340</v>
+      </c>
+      <c r="P101" s="49"/>
+      <c r="Q101" s="49" t="s">
+        <v>341</v>
+      </c>
+      <c r="R101" s="49"/>
+    </row>
+    <row r="102" spans="1:18" ht="13.65" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="4"/>
+      <c r="B102" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="C102" s="50"/>
+      <c r="D102" s="50" t="s">
+        <v>343</v>
+      </c>
+      <c r="E102" s="50"/>
+      <c r="F102" s="50" t="s">
+        <v>344</v>
+      </c>
+      <c r="G102" s="50"/>
+      <c r="H102" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="I102" s="50"/>
+      <c r="J102" s="50"/>
+      <c r="K102" s="39"/>
+      <c r="L102" s="39"/>
+      <c r="M102" s="41"/>
+      <c r="N102" s="41"/>
+      <c r="O102" s="35"/>
+      <c r="P102" s="35"/>
+      <c r="Q102" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="R102" s="50"/>
+    </row>
+    <row r="103" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="4"/>
+      <c r="B103" s="22" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="E103" s="22"/>
+      <c r="F103" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G103" s="22"/>
+      <c r="H103" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="I103" s="22"/>
+      <c r="J103" s="22"/>
+      <c r="K103" s="39"/>
+      <c r="L103" s="39"/>
+      <c r="M103" s="41"/>
+      <c r="N103" s="41"/>
+      <c r="O103" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="P103" s="22"/>
+      <c r="Q103" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="R103" s="22"/>
+    </row>
+    <row r="104" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="4"/>
+      <c r="B104" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="C104" s="22"/>
+      <c r="D104" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="E104" s="22"/>
+      <c r="F104" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="G104" s="22"/>
+      <c r="H104" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="I104" s="22"/>
+      <c r="J104" s="22"/>
+      <c r="K104" s="39"/>
+      <c r="L104" s="39"/>
+      <c r="M104" s="41"/>
+      <c r="N104" s="41"/>
+      <c r="O104" s="22" t="s">
+        <v>357</v>
+      </c>
+      <c r="P104" s="22"/>
+      <c r="Q104" s="22" t="s">
+        <v>358</v>
+      </c>
+      <c r="R104" s="22"/>
+    </row>
+    <row r="105" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="4"/>
+      <c r="B105" s="22" t="s">
+        <v>359</v>
+      </c>
+      <c r="C105" s="22"/>
+      <c r="D105" s="22" t="s">
+        <v>360</v>
+      </c>
+      <c r="E105" s="22"/>
+      <c r="F105" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="G105" s="22"/>
+      <c r="H105" s="22" t="s">
+        <v>362</v>
+      </c>
+      <c r="I105" s="22"/>
+      <c r="J105" s="22"/>
+      <c r="K105" s="39"/>
+      <c r="L105" s="39"/>
+      <c r="M105" s="41"/>
+      <c r="N105" s="41"/>
+      <c r="O105" s="22" t="s">
+        <v>363</v>
+      </c>
+      <c r="P105" s="22"/>
+      <c r="Q105" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="R105" s="22"/>
+    </row>
+    <row r="106" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="4"/>
+      <c r="B106" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="C106" s="22"/>
+      <c r="D106" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="E106" s="22"/>
+      <c r="F106" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="G106" s="22"/>
+      <c r="H106" s="22" t="s">
+        <v>368</v>
+      </c>
+      <c r="I106" s="22"/>
+      <c r="J106" s="22"/>
+      <c r="K106" s="39"/>
+      <c r="L106" s="39"/>
+      <c r="M106" s="41"/>
+      <c r="N106" s="41"/>
+      <c r="O106" s="22" t="s">
+        <v>369</v>
+      </c>
+      <c r="P106" s="22"/>
+      <c r="Q106" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="R106" s="22"/>
+    </row>
+    <row r="107" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="4"/>
+      <c r="B107" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="C107" s="22"/>
+      <c r="D107" s="22" t="s">
+        <v>372</v>
+      </c>
+      <c r="E107" s="22"/>
+      <c r="F107" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="G107" s="22"/>
+      <c r="H107" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="I107" s="22"/>
+      <c r="J107" s="22"/>
+      <c r="K107" s="39"/>
+      <c r="L107" s="39"/>
+      <c r="M107" s="41"/>
+      <c r="N107" s="41"/>
+      <c r="O107" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="P107" s="22"/>
+      <c r="Q107" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="R107" s="22"/>
+    </row>
+    <row r="108" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="4"/>
+      <c r="B108" s="22" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="22"/>
+      <c r="D108" s="22" t="s">
+        <v>378</v>
+      </c>
+      <c r="E108" s="22"/>
+      <c r="F108" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="G108" s="22"/>
+      <c r="H108" s="51" t="s">
+        <v>380</v>
+      </c>
+      <c r="I108" s="51"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="39"/>
+      <c r="L108" s="39"/>
+      <c r="M108" s="41"/>
+      <c r="N108" s="41"/>
+      <c r="O108" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="P108" s="22"/>
+      <c r="Q108" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="R108" s="22"/>
+    </row>
+    <row r="109" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="4"/>
+      <c r="B109" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="C109" s="22"/>
+      <c r="D109" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="E109" s="22"/>
+      <c r="F109" s="22" t="s">
+        <v>385</v>
+      </c>
+      <c r="G109" s="22"/>
+      <c r="H109" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="I109" s="22"/>
+      <c r="J109" s="22"/>
+      <c r="K109" s="39"/>
+      <c r="L109" s="39"/>
+      <c r="M109" s="41"/>
+      <c r="N109" s="41"/>
+      <c r="O109" s="22" t="s">
+        <v>387</v>
+      </c>
+      <c r="P109" s="22"/>
+      <c r="Q109" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="R109" s="22"/>
+    </row>
+    <row r="110" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="4"/>
+      <c r="B110" s="22" t="s">
+        <v>389</v>
+      </c>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="G110" s="22"/>
+      <c r="H110" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="I110" s="22"/>
+      <c r="J110" s="22"/>
+      <c r="K110" s="39"/>
+      <c r="L110" s="39"/>
+      <c r="M110" s="41"/>
+      <c r="N110" s="41"/>
+      <c r="O110" s="22" t="s">
+        <v>393</v>
+      </c>
+      <c r="P110" s="22"/>
+      <c r="Q110" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="R110" s="22"/>
+    </row>
+    <row r="111" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="4"/>
+      <c r="B111" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22" t="s">
+        <v>397</v>
+      </c>
+      <c r="G111" s="22"/>
+      <c r="H111" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="I111" s="22"/>
+      <c r="J111" s="22"/>
+      <c r="K111" s="39"/>
+      <c r="L111" s="39"/>
+      <c r="M111" s="41"/>
+      <c r="N111" s="41"/>
+      <c r="O111" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="P111" s="22"/>
+      <c r="Q111" s="22" t="s">
+        <v>400</v>
+      </c>
+      <c r="R111" s="22"/>
+    </row>
+    <row r="112" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="4"/>
+      <c r="B112" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="G112" s="22"/>
+      <c r="H112" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="I112" s="22"/>
+      <c r="J112" s="22"/>
+      <c r="K112" s="39"/>
+      <c r="L112" s="39"/>
+      <c r="M112" s="41"/>
+      <c r="N112" s="41"/>
+      <c r="O112" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="P112" s="22"/>
+      <c r="Q112" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="R112" s="22"/>
+    </row>
+    <row r="113" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="4"/>
+      <c r="B113" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="C113" s="22"/>
+      <c r="D113" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22" t="s">
+        <v>409</v>
+      </c>
+      <c r="G113" s="22"/>
+      <c r="H113" s="22" t="s">
+        <v>410</v>
+      </c>
+      <c r="I113" s="22"/>
+      <c r="J113" s="22"/>
+      <c r="K113" s="39"/>
+      <c r="L113" s="39"/>
+      <c r="M113" s="41"/>
+      <c r="N113" s="41"/>
+      <c r="O113" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="P113" s="22"/>
+      <c r="Q113" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="R113" s="22"/>
+    </row>
+    <row r="114" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="4"/>
+      <c r="B114" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22" t="s">
+        <v>414</v>
+      </c>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="G114" s="22"/>
+      <c r="H114" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="I114" s="22"/>
+      <c r="J114" s="22"/>
+      <c r="K114" s="39"/>
+      <c r="L114" s="39"/>
+      <c r="M114" s="41"/>
+      <c r="N114" s="41"/>
+      <c r="O114" s="22" t="s">
+        <v>415</v>
+      </c>
+      <c r="P114" s="22"/>
+      <c r="Q114" s="22" t="s">
+        <v>416</v>
+      </c>
+      <c r="R114" s="22"/>
+    </row>
+    <row r="115" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="4"/>
+      <c r="B115" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="G115" s="22"/>
+      <c r="H115" s="22" t="s">
+        <v>420</v>
+      </c>
+      <c r="I115" s="22"/>
+      <c r="J115" s="22"/>
+      <c r="K115" s="39"/>
+      <c r="L115" s="39"/>
+      <c r="M115" s="41"/>
+      <c r="N115" s="41"/>
+      <c r="O115" s="22" t="s">
+        <v>421</v>
+      </c>
+      <c r="P115" s="22"/>
+      <c r="Q115" s="22" t="s">
+        <v>422</v>
+      </c>
+      <c r="R115" s="22"/>
+    </row>
+    <row r="116" spans="1:18" ht="7.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="24"/>
+      <c r="B116" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="C116" s="22"/>
+      <c r="D116" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="E116" s="22"/>
+      <c r="F116" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="G116" s="22"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="36"/>
+      <c r="J116" s="10"/>
+      <c r="K116" s="39"/>
+      <c r="L116" s="39"/>
+      <c r="M116" s="41"/>
+      <c r="N116" s="41"/>
+      <c r="O116" s="22" t="s">
+        <v>426</v>
+      </c>
+      <c r="P116" s="22"/>
+      <c r="Q116" s="49" t="s">
+        <v>427</v>
+      </c>
+      <c r="R116" s="49"/>
+    </row>
+    <row r="117" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="24"/>
+      <c r="B117" s="22"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="22"/>
+      <c r="E117" s="22"/>
+      <c r="F117" s="22"/>
+      <c r="G117" s="22"/>
+      <c r="H117" s="50" t="s">
+        <v>428</v>
+      </c>
+      <c r="I117" s="50"/>
+      <c r="J117" s="50"/>
+      <c r="K117" s="39"/>
+      <c r="L117" s="39"/>
+      <c r="M117" s="41"/>
+      <c r="N117" s="41"/>
+      <c r="O117" s="22"/>
+      <c r="P117" s="22"/>
+      <c r="Q117" s="50" t="s">
+        <v>429</v>
+      </c>
+      <c r="R117" s="50"/>
+    </row>
+    <row r="118" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="4"/>
+      <c r="B118" s="22" t="s">
+        <v>430</v>
+      </c>
+      <c r="C118" s="22"/>
+      <c r="D118" s="22" t="s">
+        <v>431</v>
+      </c>
+      <c r="E118" s="22"/>
+      <c r="F118" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="G118" s="22"/>
+      <c r="H118" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="I118" s="22"/>
+      <c r="J118" s="22"/>
+      <c r="K118" s="39"/>
+      <c r="L118" s="39"/>
+      <c r="M118" s="41"/>
+      <c r="N118" s="41"/>
+      <c r="O118" s="22" t="s">
+        <v>434</v>
+      </c>
+      <c r="P118" s="22"/>
+      <c r="Q118" s="22" t="s">
+        <v>435</v>
+      </c>
+      <c r="R118" s="22"/>
+    </row>
+    <row r="119" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="4"/>
+      <c r="B119" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="C119" s="22"/>
+      <c r="D119" s="22" t="s">
+        <v>384</v>
+      </c>
+      <c r="E119" s="22"/>
+      <c r="F119" s="22" t="s">
+        <v>436</v>
+      </c>
+      <c r="G119" s="22"/>
+      <c r="H119" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="I119" s="22"/>
+      <c r="J119" s="22"/>
+      <c r="K119" s="39"/>
+      <c r="L119" s="39"/>
+      <c r="M119" s="41"/>
+      <c r="N119" s="41"/>
+      <c r="O119" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="P119" s="22"/>
+      <c r="Q119" s="22" t="s">
+        <v>439</v>
+      </c>
+      <c r="R119" s="22"/>
+    </row>
+    <row r="120" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="4"/>
+      <c r="B120" s="22" t="s">
+        <v>440</v>
+      </c>
+      <c r="C120" s="22"/>
+      <c r="D120" s="22" t="s">
+        <v>441</v>
+      </c>
+      <c r="E120" s="22"/>
+      <c r="F120" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="G120" s="22"/>
+      <c r="H120" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="I120" s="22"/>
+      <c r="J120" s="22"/>
+      <c r="K120" s="39"/>
+      <c r="L120" s="39"/>
+      <c r="M120" s="41"/>
+      <c r="N120" s="41"/>
+      <c r="O120" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="P120" s="22"/>
+      <c r="Q120" s="22" t="s">
+        <v>445</v>
+      </c>
+      <c r="R120" s="22"/>
+    </row>
+    <row r="121" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="4"/>
+      <c r="B121" s="22" t="s">
+        <v>446</v>
+      </c>
+      <c r="C121" s="22"/>
+      <c r="D121" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="E121" s="22"/>
+      <c r="F121" s="22" t="s">
+        <v>448</v>
+      </c>
+      <c r="G121" s="22"/>
+      <c r="H121" s="22" t="s">
+        <v>449</v>
+      </c>
+      <c r="I121" s="22"/>
+      <c r="J121" s="22"/>
+      <c r="K121" s="39"/>
+      <c r="L121" s="39"/>
+      <c r="M121" s="41"/>
+      <c r="N121" s="41"/>
+      <c r="O121" s="22" t="s">
+        <v>450</v>
+      </c>
+      <c r="P121" s="22"/>
+      <c r="Q121" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="R121" s="22"/>
+    </row>
+    <row r="122" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="4"/>
+      <c r="B122" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="C122" s="22"/>
+      <c r="D122" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="G122" s="22"/>
+      <c r="H122" s="22" t="s">
+        <v>455</v>
+      </c>
+      <c r="I122" s="22"/>
+      <c r="J122" s="22"/>
+      <c r="K122" s="39"/>
+      <c r="L122" s="39"/>
+      <c r="M122" s="41"/>
+      <c r="N122" s="41"/>
+      <c r="O122" s="22" t="s">
+        <v>456</v>
+      </c>
+      <c r="P122" s="22"/>
+      <c r="Q122" s="22" t="s">
+        <v>457</v>
+      </c>
+      <c r="R122" s="22"/>
+    </row>
+    <row r="123" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="4"/>
+      <c r="B123" s="22" t="s">
+        <v>458</v>
+      </c>
+      <c r="C123" s="22"/>
+      <c r="D123" s="22" t="s">
+        <v>459</v>
+      </c>
+      <c r="E123" s="22"/>
+      <c r="F123" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="G123" s="22"/>
+      <c r="H123" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="I123" s="22"/>
+      <c r="J123" s="22"/>
+      <c r="K123" s="39"/>
+      <c r="L123" s="39"/>
+      <c r="M123" s="41"/>
+      <c r="N123" s="41"/>
+      <c r="O123" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="P123" s="22"/>
+      <c r="Q123" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="R123" s="22"/>
+    </row>
+    <row r="124" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="4"/>
+      <c r="B124" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="C124" s="22"/>
+      <c r="D124" s="22" t="s">
+        <v>463</v>
+      </c>
+      <c r="E124" s="22"/>
+      <c r="F124" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="G124" s="22"/>
+      <c r="H124" s="22" t="s">
+        <v>465</v>
+      </c>
+      <c r="I124" s="22"/>
+      <c r="J124" s="22"/>
+      <c r="K124" s="39"/>
+      <c r="L124" s="39"/>
+      <c r="M124" s="41"/>
+      <c r="N124" s="41"/>
+      <c r="O124" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="P124" s="22"/>
+      <c r="Q124" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="R124" s="22"/>
+    </row>
+    <row r="125" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="4"/>
+      <c r="B125" s="22" t="s">
+        <v>468</v>
+      </c>
+      <c r="C125" s="22"/>
+      <c r="D125" s="22" t="s">
+        <v>469</v>
+      </c>
+      <c r="E125" s="22"/>
+      <c r="F125" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="G125" s="22"/>
+      <c r="H125" s="51" t="s">
+        <v>471</v>
+      </c>
+      <c r="I125" s="51"/>
+      <c r="J125" s="13" t="s">
+        <v>472</v>
+      </c>
+      <c r="K125" s="39"/>
+      <c r="L125" s="39"/>
+      <c r="M125" s="41"/>
+      <c r="N125" s="41"/>
+      <c r="O125" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="P125" s="22"/>
+      <c r="Q125" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="R125" s="22"/>
+    </row>
+    <row r="126" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="4"/>
+      <c r="B126" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="G126" s="22"/>
+      <c r="H126" s="51" t="s">
+        <v>478</v>
+      </c>
+      <c r="I126" s="51"/>
+      <c r="J126" s="7"/>
+      <c r="K126" s="39"/>
+      <c r="L126" s="39"/>
+      <c r="M126" s="41"/>
+      <c r="N126" s="41"/>
+      <c r="O126" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="P126" s="22"/>
+      <c r="Q126" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="R126" s="22"/>
+    </row>
+    <row r="127" spans="1:18" ht="7.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="24"/>
+      <c r="B127" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="G127" s="22"/>
+      <c r="H127" s="36"/>
+      <c r="I127" s="36"/>
+      <c r="J127" s="10"/>
+      <c r="K127" s="39"/>
+      <c r="L127" s="39"/>
+      <c r="M127" s="41"/>
+      <c r="N127" s="41"/>
+      <c r="O127" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="P127" s="22"/>
+      <c r="Q127" s="49" t="s">
+        <v>485</v>
+      </c>
+      <c r="R127" s="49"/>
+    </row>
+    <row r="128" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="24"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
+      <c r="G128" s="22"/>
+      <c r="H128" s="50" t="s">
+        <v>486</v>
+      </c>
+      <c r="I128" s="50"/>
+      <c r="J128" s="50"/>
+      <c r="K128" s="39"/>
+      <c r="L128" s="39"/>
+      <c r="M128" s="41"/>
+      <c r="N128" s="41"/>
+      <c r="O128" s="22"/>
+      <c r="P128" s="22"/>
+      <c r="Q128" s="50" t="s">
+        <v>487</v>
+      </c>
+      <c r="R128" s="50"/>
+    </row>
+    <row r="129" spans="1:18" ht="12.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="6"/>
+      <c r="B129" s="22" t="s">
+        <v>488</v>
+      </c>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="G129" s="22"/>
+      <c r="H129" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="I129" s="22"/>
+      <c r="J129" s="22"/>
+      <c r="K129" s="42"/>
+      <c r="L129" s="42"/>
+      <c r="M129" s="44"/>
+      <c r="N129" s="44"/>
+      <c r="O129" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="P129" s="22"/>
+      <c r="Q129" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="R129" s="22"/>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A130" s="8">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="635">
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="I92:J92"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:Q1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K4"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="N7:O7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:O9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="N10:O10"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="N11:O11"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="N12:O12"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="N14:O14"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="N15:O15"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="N16:O16"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="J18:K19"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="N24:O24"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="N28:O28"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="N30:O30"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="J34:K35"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="L35:O35"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:Q39"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="F37:I37"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="L37:O37"/>
-    <mergeCell ref="P37:Q37"/>
+  <mergeCells count="927">
+    <mergeCell ref="B129:C129"/>
+    <mergeCell ref="D129:E129"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="K129:L129"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="O129:P129"/>
+    <mergeCell ref="Q129:R129"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="D126:E126"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="H126:I126"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="M126:N126"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="Q126:R126"/>
+    <mergeCell ref="A127:A128"/>
+    <mergeCell ref="B127:C128"/>
+    <mergeCell ref="D127:E128"/>
+    <mergeCell ref="F127:G128"/>
+    <mergeCell ref="H127:I127"/>
+    <mergeCell ref="K127:L128"/>
+    <mergeCell ref="M127:N128"/>
+    <mergeCell ref="O127:P128"/>
+    <mergeCell ref="Q127:R127"/>
+    <mergeCell ref="H128:J128"/>
+    <mergeCell ref="Q128:R128"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="D124:E124"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="H124:J124"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="M124:N124"/>
+    <mergeCell ref="O124:P124"/>
+    <mergeCell ref="Q124:R124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="D125:E125"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="H125:I125"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="O125:P125"/>
+    <mergeCell ref="Q125:R125"/>
+    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="D122:E122"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="M122:N122"/>
+    <mergeCell ref="O122:P122"/>
+    <mergeCell ref="Q122:R122"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="D123:E123"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="H123:J123"/>
+    <mergeCell ref="K123:L123"/>
+    <mergeCell ref="M123:N123"/>
+    <mergeCell ref="O123:P123"/>
+    <mergeCell ref="Q123:R123"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="D120:E120"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="K120:L120"/>
+    <mergeCell ref="M120:N120"/>
+    <mergeCell ref="O120:P120"/>
+    <mergeCell ref="Q120:R120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="D121:E121"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="H121:J121"/>
+    <mergeCell ref="K121:L121"/>
+    <mergeCell ref="M121:N121"/>
+    <mergeCell ref="O121:P121"/>
+    <mergeCell ref="Q121:R121"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="D118:E118"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="H118:J118"/>
+    <mergeCell ref="K118:L118"/>
+    <mergeCell ref="M118:N118"/>
+    <mergeCell ref="O118:P118"/>
+    <mergeCell ref="Q118:R118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="D119:E119"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="H119:J119"/>
+    <mergeCell ref="K119:L119"/>
+    <mergeCell ref="M119:N119"/>
+    <mergeCell ref="O119:P119"/>
+    <mergeCell ref="Q119:R119"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="D115:E115"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="H115:J115"/>
+    <mergeCell ref="K115:L115"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="O115:P115"/>
+    <mergeCell ref="Q115:R115"/>
+    <mergeCell ref="A116:A117"/>
+    <mergeCell ref="B116:C117"/>
+    <mergeCell ref="D116:E117"/>
+    <mergeCell ref="F116:G117"/>
+    <mergeCell ref="H116:I116"/>
+    <mergeCell ref="K116:L117"/>
+    <mergeCell ref="M116:N117"/>
+    <mergeCell ref="O116:P117"/>
+    <mergeCell ref="Q116:R116"/>
+    <mergeCell ref="H117:J117"/>
+    <mergeCell ref="Q117:R117"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="D113:E113"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="H113:J113"/>
+    <mergeCell ref="K113:L113"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="O113:P113"/>
+    <mergeCell ref="Q113:R113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="D114:E114"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="H114:J114"/>
+    <mergeCell ref="K114:L114"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="O114:P114"/>
+    <mergeCell ref="Q114:R114"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="D111:E111"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="H111:J111"/>
+    <mergeCell ref="K111:L111"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="O111:P111"/>
+    <mergeCell ref="Q111:R111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="D112:E112"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="H112:J112"/>
+    <mergeCell ref="K112:L112"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="Q112:R112"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="D109:E109"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="H109:J109"/>
+    <mergeCell ref="K109:L109"/>
+    <mergeCell ref="M109:N109"/>
+    <mergeCell ref="O109:P109"/>
+    <mergeCell ref="Q109:R109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="D110:E110"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="H110:J110"/>
+    <mergeCell ref="K110:L110"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="O110:P110"/>
+    <mergeCell ref="Q110:R110"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="D107:E107"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="H107:J107"/>
+    <mergeCell ref="K107:L107"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="O107:P107"/>
+    <mergeCell ref="Q107:R107"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="D108:E108"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="H108:I108"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="O108:P108"/>
+    <mergeCell ref="Q108:R108"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="D105:E105"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="H105:J105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="Q105:R105"/>
+    <mergeCell ref="B106:C106"/>
+    <mergeCell ref="D106:E106"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="H106:J106"/>
+    <mergeCell ref="K106:L106"/>
+    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="O106:P106"/>
+    <mergeCell ref="Q106:R106"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="D103:E103"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="H103:J103"/>
+    <mergeCell ref="K103:L103"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="O103:P103"/>
+    <mergeCell ref="Q103:R103"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="D104:E104"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="H104:J104"/>
+    <mergeCell ref="K104:L104"/>
+    <mergeCell ref="M104:N104"/>
+    <mergeCell ref="O104:P104"/>
+    <mergeCell ref="Q104:R104"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="D101:E101"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="H101:I101"/>
+    <mergeCell ref="K101:L101"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="O101:P101"/>
+    <mergeCell ref="Q101:R101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="D102:E102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="H102:J102"/>
+    <mergeCell ref="K102:L102"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="O102:P102"/>
+    <mergeCell ref="Q102:R102"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="H99:I99"/>
+    <mergeCell ref="K99:L99"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="Q99:R99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="D100:E100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="H100:I100"/>
+    <mergeCell ref="K100:L100"/>
+    <mergeCell ref="M100:N100"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="Q100:R100"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="D97:E97"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="H97:J97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="O97:P97"/>
+    <mergeCell ref="Q97:R97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="D98:E98"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="H98:I98"/>
+    <mergeCell ref="K98:L98"/>
+    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="Q98:R98"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="D95:E95"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="H95:J95"/>
+    <mergeCell ref="K95:L95"/>
+    <mergeCell ref="M95:N95"/>
+    <mergeCell ref="O95:P95"/>
+    <mergeCell ref="Q95:R95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="D96:E96"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="H96:I96"/>
+    <mergeCell ref="K96:L96"/>
+    <mergeCell ref="M96:N96"/>
+    <mergeCell ref="O96:P96"/>
+    <mergeCell ref="Q96:R96"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:E93"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="H93:J93"/>
+    <mergeCell ref="K93:L93"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="O93:P93"/>
+    <mergeCell ref="Q93:R93"/>
+    <mergeCell ref="B94:C94"/>
+    <mergeCell ref="D94:E94"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="H94:J94"/>
+    <mergeCell ref="K94:L94"/>
+    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="O94:P94"/>
+    <mergeCell ref="Q94:R94"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:R91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:E92"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="H92:I92"/>
+    <mergeCell ref="K92:L92"/>
+    <mergeCell ref="M92:N92"/>
+    <mergeCell ref="O92:P92"/>
+    <mergeCell ref="Q92:R92"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="H88:J88"/>
+    <mergeCell ref="K88:L88"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="O88:P88"/>
+    <mergeCell ref="Q88:R88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:J89"/>
+    <mergeCell ref="K89:L89"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="O89:P89"/>
+    <mergeCell ref="Q89:R89"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="F86:J86"/>
+    <mergeCell ref="K86:L86"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="Q86:R86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="F87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="Q87:R87"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="F84:J84"/>
+    <mergeCell ref="K84:L84"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="O84:P84"/>
+    <mergeCell ref="Q84:R84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="F85:J85"/>
+    <mergeCell ref="K85:L85"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="Q85:R85"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="D81:E81"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="K81:L81"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="O81:P81"/>
+    <mergeCell ref="Q81:R81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D82:E82"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="K82:L83"/>
+    <mergeCell ref="M82:N83"/>
+    <mergeCell ref="O82:P83"/>
+    <mergeCell ref="Q82:R83"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D83:E83"/>
+    <mergeCell ref="F83:J83"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="D79:E79"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="K79:L79"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="O79:P79"/>
+    <mergeCell ref="Q79:R79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="K80:L80"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="O80:P80"/>
+    <mergeCell ref="Q80:R80"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="D77:E77"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="K77:L77"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="O77:P77"/>
+    <mergeCell ref="Q77:R77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="D78:E78"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="K78:L78"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="O78:P78"/>
+    <mergeCell ref="Q78:R78"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="D75:E75"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="K75:L75"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="Q75:R75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="D76:E76"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="K76:L76"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="O76:P76"/>
+    <mergeCell ref="Q76:R76"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="D72:E72"/>
+    <mergeCell ref="F72:J72"/>
+    <mergeCell ref="K72:L72"/>
+    <mergeCell ref="M72:N72"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="Q72:R72"/>
+    <mergeCell ref="A66:A67"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="D73:E73"/>
+    <mergeCell ref="F73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="O73:P73"/>
+    <mergeCell ref="Q73:R73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="K74:L74"/>
+    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="Q74:R74"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:P70"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="F71:J71"/>
+    <mergeCell ref="K71:L71"/>
+    <mergeCell ref="M71:P71"/>
+    <mergeCell ref="Q71:R71"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="D68:E68"/>
+    <mergeCell ref="F68:J68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="O68:P68"/>
+    <mergeCell ref="Q68:R68"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:J69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="M69:P69"/>
+    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="H65:J65"/>
+    <mergeCell ref="K65:L65"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="Q65:R65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="K66:L67"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="O66:P66"/>
+    <mergeCell ref="Q66:R66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="O67:P67"/>
+    <mergeCell ref="Q67:R67"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="Q63:R63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="H64:J64"/>
+    <mergeCell ref="K64:L64"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="O64:P64"/>
+    <mergeCell ref="Q64:R64"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:J61"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="M61:N61"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:J62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="O62:P62"/>
+    <mergeCell ref="Q62:R62"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="H59:J59"/>
+    <mergeCell ref="K59:L59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="O59:P59"/>
+    <mergeCell ref="Q59:R59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="H60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="K57:L57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="Q57:R57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="H58:J58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="O58:P58"/>
+    <mergeCell ref="Q58:R58"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F55:J55"/>
+    <mergeCell ref="K55:L55"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="O55:R55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:J56"/>
+    <mergeCell ref="K56:L56"/>
+    <mergeCell ref="M56:P56"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:J53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="M53:P53"/>
+    <mergeCell ref="Q53:R53"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="F54:J54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H51:J51"/>
+    <mergeCell ref="K51:L52"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="O51:P51"/>
+    <mergeCell ref="Q51:R51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="D52:E52"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="O52:P52"/>
+    <mergeCell ref="Q52:R52"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="D50:E50"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="H50:J50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:J47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="O47:P47"/>
+    <mergeCell ref="Q47:R47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="H48:J48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="O48:P48"/>
+    <mergeCell ref="Q48:R48"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="O44:P44"/>
+    <mergeCell ref="Q44:R44"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:R46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="H42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="O42:P42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="O43:P43"/>
+    <mergeCell ref="Q43:R43"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="D40:E40"/>
     <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="N40:Q40"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:R40"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="D41:E41"/>
     <mergeCell ref="F41:G41"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="L41:O41"/>
-    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="H41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="M41:P41"/>
+    <mergeCell ref="Q41:R41"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="D38:E38"/>
-    <mergeCell ref="F38:I38"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="N38:Q38"/>
+    <mergeCell ref="F38:J38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="O38:R38"/>
     <mergeCell ref="B39:C39"/>
     <mergeCell ref="D39:E39"/>
     <mergeCell ref="F39:G39"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:K44"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:Q46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="J47:K47"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="N47:O47"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="F48:G48"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N48:O48"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="F49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J49:K49"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="J51:K52"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="D52:E52"/>
-    <mergeCell ref="F52:G52"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:O53"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="F54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F55:I55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:Q55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:O56"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="F57:G57"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="J57:K57"/>
-    <mergeCell ref="L57:M57"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="J58:K58"/>
-    <mergeCell ref="L58:M58"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="F59:G59"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="L59:M59"/>
-    <mergeCell ref="N59:O59"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="F60:G60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="J60:K60"/>
-    <mergeCell ref="L60:M60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="J64:K64"/>
-    <mergeCell ref="L64:M64"/>
-    <mergeCell ref="N64:O64"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="J69:K69"/>
-    <mergeCell ref="L69:O69"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:G65"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="J65:K65"/>
-    <mergeCell ref="L65:M65"/>
-    <mergeCell ref="N65:O65"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="J66:K67"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="D67:E67"/>
-    <mergeCell ref="F67:G67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="L67:M67"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:I70"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="L70:O70"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="F71:I71"/>
-    <mergeCell ref="J71:K71"/>
-    <mergeCell ref="L71:O71"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="D72:E72"/>
-    <mergeCell ref="F72:I72"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="L72:M72"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="D73:E73"/>
-    <mergeCell ref="F73:I73"/>
-    <mergeCell ref="J73:K73"/>
-    <mergeCell ref="L73:M73"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="D68:E68"/>
-    <mergeCell ref="F68:I68"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="L68:M68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:I69"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="D75:E75"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="L75:M75"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="D76:E76"/>
-    <mergeCell ref="F76:G76"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="J76:K76"/>
-    <mergeCell ref="L76:M76"/>
-    <mergeCell ref="N76:O76"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="D77:E77"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="J77:K77"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="N77:O77"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="D78:E78"/>
-    <mergeCell ref="F78:G78"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="J78:K78"/>
-    <mergeCell ref="L78:M78"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="D79:E79"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="L79:M79"/>
-    <mergeCell ref="N79:O79"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="L80:M80"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="H81:I81"/>
-    <mergeCell ref="J81:K81"/>
-    <mergeCell ref="L81:M81"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="J82:K83"/>
-    <mergeCell ref="L82:M83"/>
-    <mergeCell ref="N82:O83"/>
-    <mergeCell ref="P82:Q83"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="F84:I84"/>
-    <mergeCell ref="J84:K84"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="F85:I85"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="N85:O85"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="F86:I86"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:I87"/>
-    <mergeCell ref="J87:K87"/>
-    <mergeCell ref="L87:M87"/>
-    <mergeCell ref="N87:O87"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="N88:O88"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="F89:G89"/>
-    <mergeCell ref="H89:I89"/>
-    <mergeCell ref="J89:K89"/>
-    <mergeCell ref="L89:M89"/>
-    <mergeCell ref="N89:O89"/>
-    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="H39:J39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="O39:R39"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:J36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="M36:P36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="M37:P37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="H34:J34"/>
+    <mergeCell ref="K34:L35"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="H35:J35"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="H32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:J25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="K18:L19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="H15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="H12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="Q9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="Q10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="Q8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="M5:P5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:L4"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:R1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
